--- a/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_healthcare_support_services.xlsx
+++ b/research/traditional_assets/database/data/united_arab_emirates/united_arab_emirates_healthcare_support_services.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08691190003771061</v>
+        <v>0.08672837028761633</v>
       </c>
       <c r="C2">
-        <v>238.0474331717137</v>
+        <v>236.7025788172136</v>
       </c>
       <c r="D2">
-        <v>233.5874331717137</v>
+        <v>234.6348788172136</v>
       </c>
       <c r="E2">
-        <v>-4.53</v>
+        <v>-2.1377</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.3923</v>
       </c>
       <c r="G2">
         <v>4.46</v>
@@ -1439,28 +1439,28 @@
         <v>14.83</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.12033269</v>
       </c>
       <c r="N2">
-        <v>14.83</v>
+        <v>14.70966731</v>
       </c>
       <c r="O2">
-        <v>3.7075</v>
+        <v>3.6774168275</v>
       </c>
       <c r="P2">
-        <v>11.1225</v>
+        <v>11.0322504825</v>
       </c>
       <c r="Q2">
-        <v>14.2925</v>
+        <v>14.2022504825</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08691190003771061</v>
+        <v>0.08722335382587509</v>
       </c>
       <c r="T2">
-        <v>0.8240329453738456</v>
+        <v>0.8302756192024354</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>123.2416561119011</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08672837028761633</v>
+        <v>0.08654484053752207</v>
       </c>
       <c r="C3">
-        <v>236.7025788172136</v>
+        <v>235.3671606237104</v>
       </c>
       <c r="D3">
-        <v>234.6348788172136</v>
+        <v>235.6917606237105</v>
       </c>
       <c r="E3">
-        <v>-2.1377</v>
+        <v>0.2545999999999999</v>
       </c>
       <c r="F3">
-        <v>2.3923</v>
+        <v>4.7846</v>
       </c>
       <c r="G3">
         <v>4.46</v>
@@ -1521,28 +1521,28 @@
         <v>14.83</v>
       </c>
       <c r="M3">
-        <v>0.12033269</v>
+        <v>0.24066538</v>
       </c>
       <c r="N3">
-        <v>14.70966731</v>
+        <v>14.58933462</v>
       </c>
       <c r="O3">
-        <v>3.6774168275</v>
+        <v>3.647333655</v>
       </c>
       <c r="P3">
-        <v>11.0322504825</v>
+        <v>10.942000965</v>
       </c>
       <c r="Q3">
-        <v>14.2022504825</v>
+        <v>14.112000965</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08722335382587509</v>
+        <v>0.08754116381379802</v>
       </c>
       <c r="T3">
-        <v>0.8302756192024354</v>
+        <v>0.8366456945377311</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1559,7 +1559,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>123.2416561119011</v>
+        <v>61.62082805595055</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08654484053752207</v>
+        <v>0.08636131078742779</v>
       </c>
       <c r="C4">
-        <v>235.3671606237104</v>
+        <v>234.0413066799843</v>
       </c>
       <c r="D4">
-        <v>235.6917606237105</v>
+        <v>236.7582066799843</v>
       </c>
       <c r="E4">
-        <v>0.2545999999999999</v>
+        <v>2.6469</v>
       </c>
       <c r="F4">
-        <v>4.7846</v>
+        <v>7.1769</v>
       </c>
       <c r="G4">
         <v>4.46</v>
@@ -1603,28 +1603,28 @@
         <v>14.83</v>
       </c>
       <c r="M4">
-        <v>0.24066538</v>
+        <v>0.3609980699999999</v>
       </c>
       <c r="N4">
-        <v>14.58933462</v>
+        <v>14.46900193</v>
       </c>
       <c r="O4">
-        <v>3.647333655</v>
+        <v>3.6172504825</v>
       </c>
       <c r="P4">
-        <v>10.942000965</v>
+        <v>10.8517514475</v>
       </c>
       <c r="Q4">
-        <v>14.112000965</v>
+        <v>14.0217514475</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08754116381379802</v>
+        <v>0.08786552658497709</v>
       </c>
       <c r="T4">
-        <v>0.8366456945377311</v>
+        <v>0.8431471116325172</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>61.62082805595055</v>
+        <v>41.08055203730037</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08636131078742779</v>
+        <v>0.08617778103733349</v>
       </c>
       <c r="C5">
-        <v>234.0413066799843</v>
+        <v>232.7251474036306</v>
       </c>
       <c r="D5">
-        <v>236.7582066799843</v>
+        <v>237.8343474036306</v>
       </c>
       <c r="E5">
-        <v>2.6469</v>
+        <v>5.0392</v>
       </c>
       <c r="F5">
-        <v>7.1769</v>
+        <v>9.5692</v>
       </c>
       <c r="G5">
         <v>4.46</v>
@@ -1685,28 +1685,28 @@
         <v>14.83</v>
       </c>
       <c r="M5">
-        <v>0.3609980699999999</v>
+        <v>0.48133076</v>
       </c>
       <c r="N5">
-        <v>14.46900193</v>
+        <v>14.34866924</v>
       </c>
       <c r="O5">
-        <v>3.6172504825</v>
+        <v>3.58716731</v>
       </c>
       <c r="P5">
-        <v>10.8517514475</v>
+        <v>10.76150193</v>
       </c>
       <c r="Q5">
-        <v>14.0217514475</v>
+        <v>13.93150193</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08786552658497709</v>
+        <v>0.08819664691388907</v>
       </c>
       <c r="T5">
-        <v>0.8431471116325172</v>
+        <v>0.8497839749167783</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1723,7 +1723,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>41.08055203730037</v>
+        <v>30.81041402797528</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08617778103733349</v>
+        <v>0.08599425128723923</v>
       </c>
       <c r="C6">
-        <v>232.7251474036306</v>
+        <v>231.4188155942281</v>
       </c>
       <c r="D6">
-        <v>237.8343474036306</v>
+        <v>238.9203155942281</v>
       </c>
       <c r="E6">
-        <v>5.0392</v>
+        <v>7.431500000000001</v>
       </c>
       <c r="F6">
-        <v>9.5692</v>
+        <v>11.9615</v>
       </c>
       <c r="G6">
         <v>4.46</v>
@@ -1767,28 +1767,28 @@
         <v>14.83</v>
       </c>
       <c r="M6">
-        <v>0.48133076</v>
+        <v>0.60166345</v>
       </c>
       <c r="N6">
-        <v>14.34866924</v>
+        <v>14.22833655</v>
       </c>
       <c r="O6">
-        <v>3.58716731</v>
+        <v>3.5570841375</v>
       </c>
       <c r="P6">
-        <v>10.76150193</v>
+        <v>10.6712524125</v>
       </c>
       <c r="Q6">
-        <v>13.93150193</v>
+        <v>13.8412524125</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08819664691388907</v>
+        <v>0.08853473819709393</v>
       </c>
       <c r="T6">
-        <v>0.8497839749167783</v>
+        <v>0.8565605616386027</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.81041402797528</v>
+        <v>24.64833122238022</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08599425128723923</v>
+        <v>0.08581072153714495</v>
       </c>
       <c r="C7">
-        <v>231.4188155942281</v>
+        <v>230.1224464879698</v>
       </c>
       <c r="D7">
-        <v>238.9203155942281</v>
+        <v>240.0162464879698</v>
       </c>
       <c r="E7">
-        <v>7.431500000000001</v>
+        <v>9.823799999999999</v>
       </c>
       <c r="F7">
-        <v>11.9615</v>
+        <v>14.3538</v>
       </c>
       <c r="G7">
         <v>4.46</v>
@@ -1849,28 +1849,28 @@
         <v>14.83</v>
       </c>
       <c r="M7">
-        <v>0.60166345</v>
+        <v>0.7219961399999999</v>
       </c>
       <c r="N7">
-        <v>14.22833655</v>
+        <v>14.10800386</v>
       </c>
       <c r="O7">
-        <v>3.5570841375</v>
+        <v>3.527000965</v>
       </c>
       <c r="P7">
-        <v>10.6712524125</v>
+        <v>10.581002895</v>
       </c>
       <c r="Q7">
-        <v>13.8412524125</v>
+        <v>13.751002895</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08853473819709393</v>
+        <v>0.08888002291185633</v>
       </c>
       <c r="T7">
-        <v>0.8565605616386027</v>
+        <v>0.8634813310566362</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1887,7 +1887,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.64833122238022</v>
+        <v>20.54027601865019</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08581072153714495</v>
+        <v>0.08562719178705067</v>
       </c>
       <c r="C8">
-        <v>230.1224464879698</v>
+        <v>228.8361778138046</v>
       </c>
       <c r="D8">
-        <v>240.0162464879698</v>
+        <v>241.1222778138045</v>
       </c>
       <c r="E8">
-        <v>9.823799999999999</v>
+        <v>12.2161</v>
       </c>
       <c r="F8">
-        <v>14.3538</v>
+        <v>16.7461</v>
       </c>
       <c r="G8">
         <v>4.46</v>
@@ -1931,28 +1931,28 @@
         <v>14.83</v>
       </c>
       <c r="M8">
-        <v>0.7219961399999999</v>
+        <v>0.8423288299999999</v>
       </c>
       <c r="N8">
-        <v>14.10800386</v>
+        <v>13.98767117</v>
       </c>
       <c r="O8">
-        <v>3.527000965</v>
+        <v>3.4969177925</v>
       </c>
       <c r="P8">
-        <v>10.581002895</v>
+        <v>10.4907533775</v>
       </c>
       <c r="Q8">
-        <v>13.751002895</v>
+        <v>13.6607533775</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08888002291185633</v>
+        <v>0.08923273310435556</v>
       </c>
       <c r="T8">
-        <v>0.8634813310566362</v>
+        <v>0.8705509342255949</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.54027601865019</v>
+        <v>17.60595087312873</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08562719178705067</v>
+        <v>0.08544366203695641</v>
       </c>
       <c r="C9">
-        <v>228.8361778138045</v>
+        <v>227.5601498511373</v>
       </c>
       <c r="D9">
-        <v>241.1222778138045</v>
+        <v>242.2385498511372</v>
       </c>
       <c r="E9">
-        <v>12.2161</v>
+        <v>14.6084</v>
       </c>
       <c r="F9">
-        <v>16.7461</v>
+        <v>19.1384</v>
       </c>
       <c r="G9">
         <v>4.46</v>
@@ -2013,28 +2013,28 @@
         <v>14.83</v>
       </c>
       <c r="M9">
-        <v>0.84232883</v>
+        <v>0.9626615199999999</v>
       </c>
       <c r="N9">
-        <v>13.98767117</v>
+        <v>13.86733848</v>
       </c>
       <c r="O9">
-        <v>3.4969177925</v>
+        <v>3.46683462</v>
       </c>
       <c r="P9">
-        <v>10.4907533775</v>
+        <v>10.40050386</v>
       </c>
       <c r="Q9">
-        <v>13.6607533775</v>
+        <v>13.57050386</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08923273310435556</v>
+        <v>0.08959311090973522</v>
       </c>
       <c r="T9">
-        <v>0.8705509342255949</v>
+        <v>0.8777742244199661</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.60595087312873</v>
+        <v>15.40520701398764</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08544366203695641</v>
+        <v>0.08526013228686212</v>
       </c>
       <c r="C10">
-        <v>227.5601498511373</v>
+        <v>226.2945054891414</v>
       </c>
       <c r="D10">
-        <v>242.2385498511372</v>
+        <v>243.3652054891414</v>
       </c>
       <c r="E10">
-        <v>14.6084</v>
+        <v>17.0007</v>
       </c>
       <c r="F10">
-        <v>19.1384</v>
+        <v>21.5307</v>
       </c>
       <c r="G10">
         <v>4.46</v>
@@ -2095,28 +2095,28 @@
         <v>14.83</v>
       </c>
       <c r="M10">
-        <v>0.9626615199999999</v>
+        <v>1.08299421</v>
       </c>
       <c r="N10">
-        <v>13.86733848</v>
+        <v>13.74700579</v>
       </c>
       <c r="O10">
-        <v>3.46683462</v>
+        <v>3.4367514475</v>
       </c>
       <c r="P10">
-        <v>10.40050386</v>
+        <v>10.3102543425</v>
       </c>
       <c r="Q10">
-        <v>13.57050386</v>
+        <v>13.4802543425</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08959311090973522</v>
+        <v>0.08996140910644189</v>
       </c>
       <c r="T10">
-        <v>0.8777742244199661</v>
+        <v>0.8851562682449825</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2133,7 +2133,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.40520701398764</v>
+        <v>13.69351734576679</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08526013228686212</v>
+        <v>0.08518910253676784</v>
       </c>
       <c r="C11">
-        <v>226.2945054891414</v>
+        <v>224.34106214274</v>
       </c>
       <c r="D11">
-        <v>243.3652054891414</v>
+        <v>243.80406214274</v>
       </c>
       <c r="E11">
-        <v>17.0007</v>
+        <v>19.393</v>
       </c>
       <c r="F11">
-        <v>21.5307</v>
+        <v>23.923</v>
       </c>
       <c r="G11">
         <v>4.46</v>
@@ -2177,45 +2177,45 @@
         <v>14.83</v>
       </c>
       <c r="M11">
-        <v>1.08299421</v>
+        <v>1.2392114</v>
       </c>
       <c r="N11">
-        <v>13.74700579</v>
+        <v>13.5907886</v>
       </c>
       <c r="O11">
-        <v>3.4367514475</v>
+        <v>3.39769715</v>
       </c>
       <c r="P11">
-        <v>10.3102543425</v>
+        <v>10.19309145</v>
       </c>
       <c r="Q11">
-        <v>13.4802543425</v>
+        <v>13.36309145</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08996140910644189</v>
+        <v>0.09033789170751982</v>
       </c>
       <c r="T11">
-        <v>0.8851562682449825</v>
+        <v>0.8927023574883327</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.69351734576679</v>
+        <v>11.96728822862669</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08518910253676784</v>
+        <v>0.08501682278667357</v>
       </c>
       <c r="C12">
-        <v>224.34106214274</v>
+        <v>223.0197949269714</v>
       </c>
       <c r="D12">
-        <v>243.80406214274</v>
+        <v>244.8750949269714</v>
       </c>
       <c r="E12">
-        <v>19.393</v>
+        <v>21.7853</v>
       </c>
       <c r="F12">
-        <v>23.923</v>
+        <v>26.3153</v>
       </c>
       <c r="G12">
         <v>4.46</v>
@@ -2259,28 +2259,28 @@
         <v>14.83</v>
       </c>
       <c r="M12">
-        <v>1.2392114</v>
+        <v>1.36313254</v>
       </c>
       <c r="N12">
-        <v>13.5907886</v>
+        <v>13.46686746</v>
       </c>
       <c r="O12">
-        <v>3.39769715</v>
+        <v>3.366716865</v>
       </c>
       <c r="P12">
-        <v>10.19309145</v>
+        <v>10.100150595</v>
       </c>
       <c r="Q12">
-        <v>13.36309145</v>
+        <v>13.270150595</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09033789170751982</v>
+        <v>0.09072283459176805</v>
       </c>
       <c r="T12">
-        <v>0.8927023574883327</v>
+        <v>0.9004180217708595</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2297,7 +2297,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.96728822862669</v>
+        <v>10.87935293511517</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08501682278667357</v>
+        <v>0.08484454303657929</v>
       </c>
       <c r="C13">
-        <v>223.0197949269714</v>
+        <v>221.7079793398331</v>
       </c>
       <c r="D13">
-        <v>244.8750949269714</v>
+        <v>245.9555793398331</v>
       </c>
       <c r="E13">
-        <v>21.7853</v>
+        <v>24.1776</v>
       </c>
       <c r="F13">
-        <v>26.3153</v>
+        <v>28.7076</v>
       </c>
       <c r="G13">
         <v>4.46</v>
@@ -2341,28 +2341,28 @@
         <v>14.83</v>
       </c>
       <c r="M13">
-        <v>1.36313254</v>
+        <v>1.48705368</v>
       </c>
       <c r="N13">
-        <v>13.46686746</v>
+        <v>13.34294632</v>
       </c>
       <c r="O13">
-        <v>3.366716865</v>
+        <v>3.33573658</v>
       </c>
       <c r="P13">
-        <v>10.100150595</v>
+        <v>10.00720974</v>
       </c>
       <c r="Q13">
-        <v>13.270150595</v>
+        <v>13.17720974</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09072283459176805</v>
+        <v>0.09111652617793101</v>
       </c>
       <c r="T13">
-        <v>0.9004180217708595</v>
+        <v>0.9083090420598071</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.87935293511517</v>
+        <v>9.972740190522241</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08484454303657929</v>
+        <v>0.08483801328648502</v>
       </c>
       <c r="C14">
-        <v>221.7079793398331</v>
+        <v>219.3568194576868</v>
       </c>
       <c r="D14">
-        <v>245.9555793398331</v>
+        <v>245.9967194576868</v>
       </c>
       <c r="E14">
-        <v>24.1776</v>
+        <v>26.5699</v>
       </c>
       <c r="F14">
-        <v>28.7076</v>
+        <v>31.0999</v>
       </c>
       <c r="G14">
         <v>4.46</v>
@@ -2423,45 +2423,45 @@
         <v>14.83</v>
       </c>
       <c r="M14">
-        <v>1.48705368</v>
+        <v>1.66384465</v>
       </c>
       <c r="N14">
-        <v>13.34294632</v>
+        <v>13.16615535</v>
       </c>
       <c r="O14">
-        <v>3.33573658</v>
+        <v>3.2915388375</v>
       </c>
       <c r="P14">
-        <v>10.00720974</v>
+        <v>9.874616512500001</v>
       </c>
       <c r="Q14">
-        <v>13.17720974</v>
+        <v>13.0446165125</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09111652617793101</v>
+        <v>0.09151926814538508</v>
       </c>
       <c r="T14">
-        <v>0.9083090420598071</v>
+        <v>0.916381465114018</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.972740190522241</v>
+        <v>8.913091736058412</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08483801328648502</v>
+        <v>0.08467848353639074</v>
       </c>
       <c r="C15">
-        <v>219.3568194576868</v>
+        <v>217.973915699759</v>
       </c>
       <c r="D15">
-        <v>245.9967194576868</v>
+        <v>247.006115699759</v>
       </c>
       <c r="E15">
-        <v>26.5699</v>
+        <v>28.9622</v>
       </c>
       <c r="F15">
-        <v>31.0999</v>
+        <v>33.4922</v>
       </c>
       <c r="G15">
         <v>4.46</v>
@@ -2505,28 +2505,28 @@
         <v>14.83</v>
       </c>
       <c r="M15">
-        <v>1.66384465</v>
+        <v>1.7918327</v>
       </c>
       <c r="N15">
-        <v>13.16615535</v>
+        <v>13.0381673</v>
       </c>
       <c r="O15">
-        <v>3.2915388375</v>
+        <v>3.259541825</v>
       </c>
       <c r="P15">
-        <v>9.874616512500001</v>
+        <v>9.778625475</v>
       </c>
       <c r="Q15">
-        <v>13.0446165125</v>
+        <v>12.948625475</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09151926814538508</v>
+        <v>0.09193137620510551</v>
       </c>
       <c r="T15">
-        <v>0.916381465114018</v>
+        <v>0.9246416189369314</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.913091736058412</v>
+        <v>8.276442326339952</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08467848353639074</v>
+        <v>0.08451895378629645</v>
       </c>
       <c r="C16">
-        <v>217.973915699759</v>
+        <v>216.5993297662813</v>
       </c>
       <c r="D16">
-        <v>247.006115699759</v>
+        <v>248.0238297662813</v>
       </c>
       <c r="E16">
-        <v>28.9622</v>
+        <v>31.3545</v>
       </c>
       <c r="F16">
-        <v>33.4922</v>
+        <v>35.8845</v>
       </c>
       <c r="G16">
         <v>4.46</v>
@@ -2587,28 +2587,28 @@
         <v>14.83</v>
       </c>
       <c r="M16">
-        <v>1.7918327</v>
+        <v>1.91982075</v>
       </c>
       <c r="N16">
-        <v>13.0381673</v>
+        <v>12.91017925</v>
       </c>
       <c r="O16">
-        <v>3.259541825</v>
+        <v>3.2275448125</v>
       </c>
       <c r="P16">
-        <v>9.778625475</v>
+        <v>9.682634437500001</v>
       </c>
       <c r="Q16">
-        <v>12.948625475</v>
+        <v>12.8526344375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09193137620510551</v>
+        <v>0.09235318092505465</v>
       </c>
       <c r="T16">
-        <v>0.9246416189369314</v>
+        <v>0.933096129320384</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.276442326339952</v>
+        <v>7.724679504583956</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08451895378629645</v>
+        <v>0.08445542403620217</v>
       </c>
       <c r="C17">
-        <v>216.5993297662813</v>
+        <v>214.6146541117735</v>
       </c>
       <c r="D17">
-        <v>248.0238297662813</v>
+        <v>248.4314541117735</v>
       </c>
       <c r="E17">
-        <v>31.35449999999999</v>
+        <v>33.7468</v>
       </c>
       <c r="F17">
-        <v>35.8845</v>
+        <v>38.2768</v>
       </c>
       <c r="G17">
         <v>4.46</v>
@@ -2669,45 +2669,45 @@
         <v>14.83</v>
       </c>
       <c r="M17">
-        <v>1.91982075</v>
+        <v>2.07843024</v>
       </c>
       <c r="N17">
-        <v>12.91017925</v>
+        <v>12.75156976</v>
       </c>
       <c r="O17">
-        <v>3.2275448125</v>
+        <v>3.18789244</v>
       </c>
       <c r="P17">
-        <v>9.682634437500001</v>
+        <v>9.56367732</v>
       </c>
       <c r="Q17">
-        <v>12.8526344375</v>
+        <v>12.73367732</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09235318092505465</v>
+        <v>0.09278502861452641</v>
       </c>
       <c r="T17">
-        <v>0.933096129320384</v>
+        <v>0.9417519375701092</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.25</v>
       </c>
       <c r="W17">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.724679504583958</v>
+        <v>7.135192567252099</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08445542403620217</v>
+        <v>0.0843018942861079</v>
       </c>
       <c r="C18">
-        <v>214.6146541117735</v>
+        <v>213.2129967742333</v>
       </c>
       <c r="D18">
-        <v>248.4314541117735</v>
+        <v>249.4220967742333</v>
       </c>
       <c r="E18">
-        <v>33.7468</v>
+        <v>36.1391</v>
       </c>
       <c r="F18">
-        <v>38.2768</v>
+        <v>40.6691</v>
       </c>
       <c r="G18">
         <v>4.46</v>
@@ -2751,28 +2751,28 @@
         <v>14.83</v>
       </c>
       <c r="M18">
-        <v>2.07843024</v>
+        <v>2.20833213</v>
       </c>
       <c r="N18">
-        <v>12.75156976</v>
+        <v>12.62166787</v>
       </c>
       <c r="O18">
-        <v>3.18789244</v>
+        <v>3.1554169675</v>
       </c>
       <c r="P18">
-        <v>9.56367732</v>
+        <v>9.466250902500001</v>
       </c>
       <c r="Q18">
-        <v>12.73367732</v>
+        <v>12.6362509025</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09278502861452641</v>
+        <v>0.09322728227241917</v>
       </c>
       <c r="T18">
-        <v>0.9417519375701092</v>
+        <v>0.9506163195125992</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.135192567252099</v>
+        <v>6.715475357413742</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0843018942861079</v>
+        <v>0.08414836453601363</v>
       </c>
       <c r="C19">
-        <v>213.2129967742333</v>
+        <v>211.8192716195771</v>
       </c>
       <c r="D19">
-        <v>249.4220967742333</v>
+        <v>250.4206716195771</v>
       </c>
       <c r="E19">
-        <v>36.1391</v>
+        <v>38.5314</v>
       </c>
       <c r="F19">
-        <v>40.6691</v>
+        <v>43.06140000000001</v>
       </c>
       <c r="G19">
         <v>4.46</v>
@@ -2833,28 +2833,28 @@
         <v>14.83</v>
       </c>
       <c r="M19">
-        <v>2.20833213</v>
+        <v>2.33823402</v>
       </c>
       <c r="N19">
-        <v>12.62166787</v>
+        <v>12.49176598</v>
       </c>
       <c r="O19">
-        <v>3.1554169675</v>
+        <v>3.122941495</v>
       </c>
       <c r="P19">
-        <v>9.466250902500001</v>
+        <v>9.368824485000001</v>
       </c>
       <c r="Q19">
-        <v>12.6362509025</v>
+        <v>12.538824485</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09322728227241917</v>
+        <v>0.09368032260489467</v>
       </c>
       <c r="T19">
-        <v>0.9506163195125992</v>
+        <v>0.9596969058927104</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.715475357413742</v>
+        <v>6.342393393112978</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08414836453601364</v>
+        <v>0.08413733478591937</v>
       </c>
       <c r="C20">
-        <v>211.819271619577</v>
+        <v>209.4990182926655</v>
       </c>
       <c r="D20">
-        <v>250.420671619577</v>
+        <v>250.4927182926655</v>
       </c>
       <c r="E20">
-        <v>38.5314</v>
+        <v>40.9237</v>
       </c>
       <c r="F20">
-        <v>43.0614</v>
+        <v>45.4537</v>
       </c>
       <c r="G20">
         <v>4.46</v>
@@ -2915,45 +2915,45 @@
         <v>14.83</v>
       </c>
       <c r="M20">
-        <v>2.33823402</v>
+        <v>2.51358961</v>
       </c>
       <c r="N20">
-        <v>12.49176598</v>
+        <v>12.31641039</v>
       </c>
       <c r="O20">
-        <v>3.122941495</v>
+        <v>3.0791025975</v>
       </c>
       <c r="P20">
-        <v>9.368824485000001</v>
+        <v>9.237307792499999</v>
       </c>
       <c r="Q20">
-        <v>12.538824485</v>
+        <v>12.4073077925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09368032260489467</v>
+        <v>0.09414454911841896</v>
       </c>
       <c r="T20">
-        <v>0.9596969058927104</v>
+        <v>0.9690017042822074</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.25</v>
       </c>
       <c r="W20">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.342393393112979</v>
+        <v>5.899928906851266</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08413733478591937</v>
+        <v>0.08399130503582508</v>
       </c>
       <c r="C21">
-        <v>209.4990182926655</v>
+        <v>208.0645119323016</v>
       </c>
       <c r="D21">
-        <v>250.4927182926655</v>
+        <v>251.4505119323016</v>
       </c>
       <c r="E21">
-        <v>40.9237</v>
+        <v>43.316</v>
       </c>
       <c r="F21">
-        <v>45.4537</v>
+        <v>47.846</v>
       </c>
       <c r="G21">
         <v>4.46</v>
@@ -2997,28 +2997,28 @@
         <v>14.83</v>
       </c>
       <c r="M21">
-        <v>2.51358961</v>
+        <v>2.6458838</v>
       </c>
       <c r="N21">
-        <v>12.31641039</v>
+        <v>12.1841162</v>
       </c>
       <c r="O21">
-        <v>3.0791025975</v>
+        <v>3.04602905</v>
       </c>
       <c r="P21">
-        <v>9.237307792499999</v>
+        <v>9.13808715</v>
       </c>
       <c r="Q21">
-        <v>12.4073077925</v>
+        <v>12.30808715</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09414454911841896</v>
+        <v>0.09462038129478134</v>
       </c>
       <c r="T21">
-        <v>0.9690017042822074</v>
+        <v>0.9785391226314417</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.899928906851266</v>
+        <v>5.604932461508702</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08399130503582508</v>
+        <v>0.08384527528573081</v>
       </c>
       <c r="C22">
-        <v>208.0645119323016</v>
+        <v>206.6373581992894</v>
       </c>
       <c r="D22">
-        <v>251.4505119323016</v>
+        <v>252.4156581992895</v>
       </c>
       <c r="E22">
-        <v>43.316</v>
+        <v>45.7083</v>
       </c>
       <c r="F22">
-        <v>47.846</v>
+        <v>50.2383</v>
       </c>
       <c r="G22">
         <v>4.46</v>
@@ -3079,28 +3079,28 @@
         <v>14.83</v>
       </c>
       <c r="M22">
-        <v>2.6458838</v>
+        <v>2.77817799</v>
       </c>
       <c r="N22">
-        <v>12.1841162</v>
+        <v>12.05182201</v>
       </c>
       <c r="O22">
-        <v>3.04602905</v>
+        <v>3.0129555025</v>
       </c>
       <c r="P22">
-        <v>9.13808715</v>
+        <v>9.0388665075</v>
       </c>
       <c r="Q22">
-        <v>12.30808715</v>
+        <v>12.2088665075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09462038129478134</v>
+        <v>0.09510825985535545</v>
       </c>
       <c r="T22">
-        <v>0.9785391226314417</v>
+        <v>0.9883179946097705</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.604932461508702</v>
+        <v>5.338030915722574</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08384527528573081</v>
+        <v>0.08369924553563651</v>
       </c>
       <c r="C23">
-        <v>206.6373581992895</v>
+        <v>205.217642084952</v>
       </c>
       <c r="D23">
-        <v>252.4156581992895</v>
+        <v>253.3882420849521</v>
       </c>
       <c r="E23">
-        <v>45.70829999999999</v>
+        <v>48.1006</v>
       </c>
       <c r="F23">
-        <v>50.2383</v>
+        <v>52.6306</v>
       </c>
       <c r="G23">
         <v>4.46</v>
@@ -3161,28 +3161,28 @@
         <v>14.83</v>
       </c>
       <c r="M23">
-        <v>2.77817799</v>
+        <v>2.91047218</v>
       </c>
       <c r="N23">
-        <v>12.05182201</v>
+        <v>11.91952782</v>
       </c>
       <c r="O23">
-        <v>3.0129555025</v>
+        <v>2.979881955</v>
       </c>
       <c r="P23">
-        <v>9.0388665075</v>
+        <v>8.939645864999999</v>
       </c>
       <c r="Q23">
-        <v>12.2088665075</v>
+        <v>12.109645865</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09510825985535545</v>
+        <v>0.09560864812261093</v>
       </c>
       <c r="T23">
-        <v>0.9883179946097705</v>
+        <v>0.9983476068952359</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.338030915722575</v>
+        <v>5.095393146826093</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08369924553563651</v>
+        <v>0.08355321578554224</v>
       </c>
       <c r="C24">
-        <v>205.217642084952</v>
+        <v>203.8054498956001</v>
       </c>
       <c r="D24">
-        <v>253.3882420849521</v>
+        <v>254.3683498956001</v>
       </c>
       <c r="E24">
-        <v>48.1006</v>
+        <v>50.4929</v>
       </c>
       <c r="F24">
-        <v>52.6306</v>
+        <v>55.0229</v>
       </c>
       <c r="G24">
         <v>4.46</v>
@@ -3243,28 +3243,28 @@
         <v>14.83</v>
       </c>
       <c r="M24">
-        <v>2.91047218</v>
+        <v>3.04276637</v>
       </c>
       <c r="N24">
-        <v>11.91952782</v>
+        <v>11.78723363</v>
       </c>
       <c r="O24">
-        <v>2.979881955</v>
+        <v>2.9468084075</v>
       </c>
       <c r="P24">
-        <v>8.939645864999999</v>
+        <v>8.840425222499999</v>
       </c>
       <c r="Q24">
-        <v>12.109645865</v>
+        <v>12.0104252225</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09560864812261093</v>
+        <v>0.0961220334877172</v>
       </c>
       <c r="T24">
-        <v>0.9983476068952359</v>
+        <v>1.008637728590714</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.095393146826093</v>
+        <v>4.873854314355393</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08355321578554224</v>
+        <v>0.08340718603544799</v>
       </c>
       <c r="C25">
-        <v>203.8054498956001</v>
+        <v>202.4008692780642</v>
       </c>
       <c r="D25">
-        <v>254.3683498956001</v>
+        <v>255.3560692780642</v>
       </c>
       <c r="E25">
-        <v>50.4929</v>
+        <v>52.8852</v>
       </c>
       <c r="F25">
-        <v>55.0229</v>
+        <v>57.4152</v>
       </c>
       <c r="G25">
         <v>4.46</v>
@@ -3325,28 +3325,28 @@
         <v>14.83</v>
       </c>
       <c r="M25">
-        <v>3.04276637</v>
+        <v>3.17506056</v>
       </c>
       <c r="N25">
-        <v>11.78723363</v>
+        <v>11.65493944</v>
       </c>
       <c r="O25">
-        <v>2.9468084075</v>
+        <v>2.91373486</v>
       </c>
       <c r="P25">
-        <v>8.840425222499999</v>
+        <v>8.74120458</v>
       </c>
       <c r="Q25">
-        <v>12.0104252225</v>
+        <v>11.91120458</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.0961220334877172</v>
+        <v>0.09664892899401049</v>
       </c>
       <c r="T25">
-        <v>1.008637728590714</v>
+        <v>1.019198642962388</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.873854314355393</v>
+        <v>4.670777051257252</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08340718603544799</v>
+        <v>0.08372990628535369</v>
       </c>
       <c r="C26">
-        <v>202.4008692780642</v>
+        <v>197.8359149648059</v>
       </c>
       <c r="D26">
-        <v>255.3560692780642</v>
+        <v>253.1834149648059</v>
       </c>
       <c r="E26">
-        <v>52.8852</v>
+        <v>55.2775</v>
       </c>
       <c r="F26">
-        <v>57.4152</v>
+        <v>59.8075</v>
       </c>
       <c r="G26">
         <v>4.46</v>
@@ -3407,45 +3407,45 @@
         <v>14.83</v>
       </c>
       <c r="M26">
-        <v>3.17506056</v>
+        <v>3.4568735</v>
       </c>
       <c r="N26">
-        <v>11.65493944</v>
+        <v>11.3731265</v>
       </c>
       <c r="O26">
-        <v>2.91373486</v>
+        <v>2.843281625</v>
       </c>
       <c r="P26">
-        <v>8.74120458</v>
+        <v>8.529844875</v>
       </c>
       <c r="Q26">
-        <v>11.91120458</v>
+        <v>11.699844875</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09664892899401049</v>
+        <v>0.09718987504713826</v>
       </c>
       <c r="T26">
-        <v>1.019198642962388</v>
+        <v>1.030041181717307</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.25</v>
       </c>
       <c r="W26">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.670777051257252</v>
+        <v>4.290003669500779</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08372990628535369</v>
+        <v>0.08360262653525942</v>
       </c>
       <c r="C27">
-        <v>197.8359149648059</v>
+        <v>196.2960721810969</v>
       </c>
       <c r="D27">
-        <v>253.1834149648059</v>
+        <v>254.0358721810969</v>
       </c>
       <c r="E27">
-        <v>55.2775</v>
+        <v>57.6698</v>
       </c>
       <c r="F27">
-        <v>59.8075</v>
+        <v>62.1998</v>
       </c>
       <c r="G27">
         <v>4.46</v>
@@ -3489,28 +3489,28 @@
         <v>14.83</v>
       </c>
       <c r="M27">
-        <v>3.4568735</v>
+        <v>3.59514844</v>
       </c>
       <c r="N27">
-        <v>11.3731265</v>
+        <v>11.23485156</v>
       </c>
       <c r="O27">
-        <v>2.843281625</v>
+        <v>2.80871289</v>
       </c>
       <c r="P27">
-        <v>8.529844875</v>
+        <v>8.42613867</v>
       </c>
       <c r="Q27">
-        <v>11.699844875</v>
+        <v>11.59613867</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09718987504713826</v>
+        <v>0.09774544126386409</v>
       </c>
       <c r="T27">
-        <v>1.030041181717307</v>
+        <v>1.041176762060197</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.290003669500779</v>
+        <v>4.125003528366133</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08360262653525942</v>
+        <v>0.08418409678516516</v>
       </c>
       <c r="C28">
-        <v>196.2960721810969</v>
+        <v>190.0554517970348</v>
       </c>
       <c r="D28">
-        <v>254.0358721810969</v>
+        <v>250.1875517970348</v>
       </c>
       <c r="E28">
-        <v>57.6698</v>
+        <v>60.0621</v>
       </c>
       <c r="F28">
-        <v>62.1998</v>
+        <v>64.5921</v>
       </c>
       <c r="G28">
         <v>4.46</v>
@@ -3571,45 +3571,45 @@
         <v>14.83</v>
       </c>
       <c r="M28">
-        <v>3.59514844</v>
+        <v>3.95949573</v>
       </c>
       <c r="N28">
-        <v>11.23485156</v>
+        <v>10.87050427</v>
       </c>
       <c r="O28">
-        <v>2.80871289</v>
+        <v>2.7176260675</v>
       </c>
       <c r="P28">
-        <v>8.42613867</v>
+        <v>8.1528782025</v>
       </c>
       <c r="Q28">
-        <v>11.59613867</v>
+        <v>11.3228782025</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09774544126386409</v>
+        <v>0.09831622847282898</v>
       </c>
       <c r="T28">
-        <v>1.041176762060197</v>
+        <v>1.052617426796043</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.125003528366133</v>
+        <v>3.74542644095742</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08418409678516516</v>
+        <v>0.08408306703507087</v>
       </c>
       <c r="C29">
-        <v>190.0554517970348</v>
+        <v>188.3234015573688</v>
       </c>
       <c r="D29">
-        <v>250.1875517970348</v>
+        <v>250.8478015573687</v>
       </c>
       <c r="E29">
-        <v>60.0621</v>
+        <v>62.45440000000001</v>
       </c>
       <c r="F29">
-        <v>64.5921</v>
+        <v>66.98440000000001</v>
       </c>
       <c r="G29">
         <v>4.46</v>
@@ -3653,28 +3653,28 @@
         <v>14.83</v>
       </c>
       <c r="M29">
-        <v>3.95949573</v>
+        <v>4.10614372</v>
       </c>
       <c r="N29">
-        <v>10.87050427</v>
+        <v>10.72385628</v>
       </c>
       <c r="O29">
-        <v>2.7176260675</v>
+        <v>2.68096407</v>
       </c>
       <c r="P29">
-        <v>8.1528782025</v>
+        <v>8.04289221</v>
       </c>
       <c r="Q29">
-        <v>11.3228782025</v>
+        <v>11.21289221</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09831622847282898</v>
+        <v>0.09890287088204287</v>
       </c>
       <c r="T29">
-        <v>1.052617426796043</v>
+        <v>1.064375887774551</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.74542644095742</v>
+        <v>3.611661210923226</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08408306703507087</v>
+        <v>0.08459103728497659</v>
       </c>
       <c r="C30">
-        <v>188.3234015573688</v>
+        <v>182.6462391416183</v>
       </c>
       <c r="D30">
-        <v>250.8478015573687</v>
+        <v>247.5629391416182</v>
       </c>
       <c r="E30">
-        <v>62.45440000000001</v>
+        <v>64.8467</v>
       </c>
       <c r="F30">
-        <v>66.98440000000001</v>
+        <v>69.3767</v>
       </c>
       <c r="G30">
         <v>4.46</v>
@@ -3735,45 +3735,45 @@
         <v>14.83</v>
       </c>
       <c r="M30">
-        <v>4.10614372</v>
+        <v>4.44704647</v>
       </c>
       <c r="N30">
-        <v>10.72385628</v>
+        <v>10.38295353</v>
       </c>
       <c r="O30">
-        <v>2.68096407</v>
+        <v>2.5957383825</v>
       </c>
       <c r="P30">
-        <v>8.04289221</v>
+        <v>7.7872151475</v>
       </c>
       <c r="Q30">
-        <v>11.21289221</v>
+        <v>10.9572151475</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09890287088204287</v>
+        <v>0.0995060384295445</v>
       </c>
       <c r="T30">
-        <v>1.064375887774551</v>
+        <v>1.076465573005974</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.611661210923226</v>
+        <v>3.334797623556203</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08459103728497659</v>
+        <v>0.0845110075348823</v>
       </c>
       <c r="C31">
-        <v>182.6462391416183</v>
+        <v>180.7657418926642</v>
       </c>
       <c r="D31">
-        <v>247.5629391416182</v>
+        <v>248.0747418926642</v>
       </c>
       <c r="E31">
-        <v>64.84669999999998</v>
+        <v>67.23899999999999</v>
       </c>
       <c r="F31">
-        <v>69.37669999999999</v>
+        <v>71.76899999999999</v>
       </c>
       <c r="G31">
         <v>4.46</v>
@@ -3817,28 +3817,28 @@
         <v>14.83</v>
       </c>
       <c r="M31">
-        <v>4.447046469999999</v>
+        <v>4.6003929</v>
       </c>
       <c r="N31">
-        <v>10.38295353</v>
+        <v>10.2296071</v>
       </c>
       <c r="O31">
-        <v>2.5957383825</v>
+        <v>2.557401775</v>
       </c>
       <c r="P31">
-        <v>7.787215147500001</v>
+        <v>7.672205324999999</v>
       </c>
       <c r="Q31">
-        <v>10.9572151475</v>
+        <v>10.842205325</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0995060384295445</v>
+        <v>0.1001264393355462</v>
       </c>
       <c r="T31">
-        <v>1.076465573005974</v>
+        <v>1.088900677815439</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.334797623556204</v>
+        <v>3.223637702770996</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.0845110075348823</v>
+        <v>0.08443097778478804</v>
       </c>
       <c r="C32">
-        <v>180.7657418926642</v>
+        <v>178.8873651930002</v>
       </c>
       <c r="D32">
-        <v>248.0747418926642</v>
+        <v>248.5886651930002</v>
       </c>
       <c r="E32">
-        <v>67.23899999999999</v>
+        <v>69.6313</v>
       </c>
       <c r="F32">
-        <v>71.76899999999999</v>
+        <v>74.1613</v>
       </c>
       <c r="G32">
         <v>4.46</v>
@@ -3899,28 +3899,28 @@
         <v>14.83</v>
       </c>
       <c r="M32">
-        <v>4.6003929</v>
+        <v>4.75373933</v>
       </c>
       <c r="N32">
-        <v>10.2296071</v>
+        <v>10.07626067</v>
       </c>
       <c r="O32">
-        <v>2.557401775</v>
+        <v>2.5190651675</v>
       </c>
       <c r="P32">
-        <v>7.672205324999999</v>
+        <v>7.5571955025</v>
       </c>
       <c r="Q32">
-        <v>10.842205325</v>
+        <v>10.7271955025</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1001264393355462</v>
+        <v>0.1007648228765044</v>
       </c>
       <c r="T32">
-        <v>1.088900677815439</v>
+        <v>1.101696220445467</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.223637702770996</v>
+        <v>3.119649389778383</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08443097778478804</v>
+        <v>0.08435094803469376</v>
       </c>
       <c r="C33">
-        <v>178.8873651930002</v>
+        <v>177.0111222490748</v>
       </c>
       <c r="D33">
-        <v>248.5886651930002</v>
+        <v>249.1047222490748</v>
       </c>
       <c r="E33">
-        <v>69.6313</v>
+        <v>72.0236</v>
       </c>
       <c r="F33">
-        <v>74.1613</v>
+        <v>76.5536</v>
       </c>
       <c r="G33">
         <v>4.46</v>
@@ -3981,28 +3981,28 @@
         <v>14.83</v>
       </c>
       <c r="M33">
-        <v>4.75373933</v>
+        <v>4.90708576</v>
       </c>
       <c r="N33">
-        <v>10.07626067</v>
+        <v>9.922914240000001</v>
       </c>
       <c r="O33">
-        <v>2.5190651675</v>
+        <v>2.48072856</v>
       </c>
       <c r="P33">
-        <v>7.5571955025</v>
+        <v>7.442185680000001</v>
       </c>
       <c r="Q33">
-        <v>10.7271955025</v>
+        <v>10.61218568</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1007648228765044</v>
+        <v>0.1014219824039614</v>
       </c>
       <c r="T33">
-        <v>1.101696220445467</v>
+        <v>1.114868102564615</v>
       </c>
       <c r="U33">
         <v>0.0641</v>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.119649389778383</v>
+        <v>3.022160346347809</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08435094803469376</v>
+        <v>0.08620141828459948</v>
       </c>
       <c r="C34">
-        <v>177.0111222490748</v>
+        <v>163.2093000786946</v>
       </c>
       <c r="D34">
-        <v>249.1047222490748</v>
+        <v>237.6952000786946</v>
       </c>
       <c r="E34">
-        <v>72.0236</v>
+        <v>74.41589999999999</v>
       </c>
       <c r="F34">
-        <v>76.5536</v>
+        <v>78.94589999999999</v>
       </c>
       <c r="G34">
         <v>4.46</v>
@@ -4063,45 +4063,45 @@
         <v>14.83</v>
       </c>
       <c r="M34">
-        <v>4.90708576</v>
+        <v>5.67621021</v>
       </c>
       <c r="N34">
-        <v>9.922914240000001</v>
+        <v>9.153789790000001</v>
       </c>
       <c r="O34">
-        <v>2.48072856</v>
+        <v>2.2884474475</v>
       </c>
       <c r="P34">
-        <v>7.442185680000001</v>
+        <v>6.865342342500001</v>
       </c>
       <c r="Q34">
-        <v>10.61218568</v>
+        <v>10.0353423425</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1014219824039614</v>
+        <v>0.1020987586337306</v>
       </c>
       <c r="T34">
-        <v>1.114868102564615</v>
+        <v>1.128433175194781</v>
       </c>
       <c r="U34">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V34">
         <v>0.25</v>
       </c>
       <c r="W34">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.022160346347809</v>
+        <v>2.612658702081437</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08620141828459948</v>
+        <v>0.0861798885345052</v>
       </c>
       <c r="C35">
-        <v>163.2093000786946</v>
+        <v>160.9437344120975</v>
       </c>
       <c r="D35">
-        <v>237.6952000786946</v>
+        <v>237.8219344120975</v>
       </c>
       <c r="E35">
-        <v>74.41589999999999</v>
+        <v>76.8082</v>
       </c>
       <c r="F35">
-        <v>78.94589999999999</v>
+        <v>81.3382</v>
       </c>
       <c r="G35">
         <v>4.46</v>
@@ -4145,28 +4145,28 @@
         <v>14.83</v>
       </c>
       <c r="M35">
-        <v>5.67621021</v>
+        <v>5.848216580000001</v>
       </c>
       <c r="N35">
-        <v>9.153789790000001</v>
+        <v>8.981783419999999</v>
       </c>
       <c r="O35">
-        <v>2.2884474475</v>
+        <v>2.245445855</v>
       </c>
       <c r="P35">
-        <v>6.865342342500001</v>
+        <v>6.736337564999999</v>
       </c>
       <c r="Q35">
-        <v>10.0353423425</v>
+        <v>9.906337564999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1020987586337306</v>
+        <v>0.1027960432340988</v>
       </c>
       <c r="T35">
-        <v>1.128433175194781</v>
+        <v>1.142409310631922</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.612658702081437</v>
+        <v>2.535815799079042</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0861798885345052</v>
+        <v>0.08718210878441092</v>
       </c>
       <c r="C36">
-        <v>160.9437344120975</v>
+        <v>152.791699938891</v>
       </c>
       <c r="D36">
-        <v>237.8219344120975</v>
+        <v>232.062199938891</v>
       </c>
       <c r="E36">
-        <v>76.8082</v>
+        <v>79.20050000000001</v>
       </c>
       <c r="F36">
-        <v>81.3382</v>
+        <v>83.73050000000001</v>
       </c>
       <c r="G36">
         <v>4.46</v>
@@ -4227,45 +4227,45 @@
         <v>14.83</v>
       </c>
       <c r="M36">
-        <v>5.848216580000001</v>
+        <v>6.346771900000001</v>
       </c>
       <c r="N36">
-        <v>8.981783419999999</v>
+        <v>8.483228099999998</v>
       </c>
       <c r="O36">
-        <v>2.245445855</v>
+        <v>2.120807025</v>
       </c>
       <c r="P36">
-        <v>6.736337564999999</v>
+        <v>6.362421074999999</v>
       </c>
       <c r="Q36">
-        <v>9.906337564999999</v>
+        <v>9.532421074999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1027960432340988</v>
+        <v>0.1035147827452476</v>
       </c>
       <c r="T36">
-        <v>1.142409310631922</v>
+        <v>1.156815481005591</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.535815799079042</v>
+        <v>2.336620920628957</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08718210878441092</v>
+        <v>0.08718982903431666</v>
       </c>
       <c r="C37">
-        <v>152.791699938891</v>
+        <v>150.3561144695135</v>
       </c>
       <c r="D37">
-        <v>232.062199938891</v>
+        <v>232.0189144695135</v>
       </c>
       <c r="E37">
-        <v>79.20050000000001</v>
+        <v>81.59280000000001</v>
       </c>
       <c r="F37">
-        <v>83.73050000000001</v>
+        <v>86.12280000000001</v>
       </c>
       <c r="G37">
         <v>4.46</v>
@@ -4309,28 +4309,28 @@
         <v>14.83</v>
       </c>
       <c r="M37">
-        <v>6.346771900000001</v>
+        <v>6.528108240000002</v>
       </c>
       <c r="N37">
-        <v>8.483228099999998</v>
+        <v>8.301891759999998</v>
       </c>
       <c r="O37">
-        <v>2.120807025</v>
+        <v>2.07547294</v>
       </c>
       <c r="P37">
-        <v>6.362421074999999</v>
+        <v>6.226418819999999</v>
       </c>
       <c r="Q37">
-        <v>9.532421074999998</v>
+        <v>9.396418819999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1035147827452476</v>
+        <v>0.1042559828661198</v>
       </c>
       <c r="T37">
-        <v>1.156815481005591</v>
+        <v>1.171671844203437</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.336620920628957</v>
+        <v>2.27171478394482</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08718982903431666</v>
+        <v>0.08719754928422237</v>
       </c>
       <c r="C38">
-        <v>150.3561144695136</v>
+        <v>147.9205451447944</v>
       </c>
       <c r="D38">
-        <v>232.0189144695135</v>
+        <v>231.9756451447944</v>
       </c>
       <c r="E38">
-        <v>81.5928</v>
+        <v>83.98509999999999</v>
       </c>
       <c r="F38">
-        <v>86.1228</v>
+        <v>88.51509999999999</v>
       </c>
       <c r="G38">
         <v>4.46</v>
@@ -4391,28 +4391,28 @@
         <v>14.83</v>
       </c>
       <c r="M38">
-        <v>6.528108240000001</v>
+        <v>6.70944458</v>
       </c>
       <c r="N38">
-        <v>8.30189176</v>
+        <v>8.120555420000001</v>
       </c>
       <c r="O38">
-        <v>2.07547294</v>
+        <v>2.030138855</v>
       </c>
       <c r="P38">
-        <v>6.22641882</v>
+        <v>6.090416565</v>
       </c>
       <c r="Q38">
-        <v>9.396418820000001</v>
+        <v>9.260416565</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1042559828661198</v>
+        <v>0.1050207131495593</v>
       </c>
       <c r="T38">
-        <v>1.171671844203437</v>
+        <v>1.186999837978992</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.27171478394482</v>
+        <v>2.210317087081447</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08719754928422237</v>
+        <v>0.08720526953412809</v>
       </c>
       <c r="C39">
-        <v>147.9205451447944</v>
+        <v>145.4849919557025</v>
       </c>
       <c r="D39">
-        <v>231.9756451447944</v>
+        <v>231.9323919557025</v>
       </c>
       <c r="E39">
-        <v>83.98509999999999</v>
+        <v>86.37739999999999</v>
       </c>
       <c r="F39">
-        <v>88.51509999999999</v>
+        <v>90.9074</v>
       </c>
       <c r="G39">
         <v>4.46</v>
@@ -4473,28 +4473,28 @@
         <v>14.83</v>
       </c>
       <c r="M39">
-        <v>6.70944458</v>
+        <v>6.89078092</v>
       </c>
       <c r="N39">
-        <v>8.120555420000001</v>
+        <v>7.93921908</v>
       </c>
       <c r="O39">
-        <v>2.030138855</v>
+        <v>1.98480477</v>
       </c>
       <c r="P39">
-        <v>6.090416565</v>
+        <v>5.95441431</v>
       </c>
       <c r="Q39">
-        <v>9.260416565</v>
+        <v>9.124414309999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1050207131495593</v>
+        <v>0.1058101121518195</v>
       </c>
       <c r="T39">
-        <v>1.186999837978992</v>
+        <v>1.202822283166662</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.210317087081447</v>
+        <v>2.152150847947724</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08720526953412809</v>
+        <v>0.08721298978403383</v>
       </c>
       <c r="C40">
-        <v>145.4849919557025</v>
+        <v>143.0494548932139</v>
       </c>
       <c r="D40">
-        <v>231.9323919557025</v>
+        <v>231.8891548932139</v>
       </c>
       <c r="E40">
-        <v>86.37739999999999</v>
+        <v>88.7697</v>
       </c>
       <c r="F40">
-        <v>90.9074</v>
+        <v>93.2997</v>
       </c>
       <c r="G40">
         <v>4.46</v>
@@ -4555,28 +4555,28 @@
         <v>14.83</v>
       </c>
       <c r="M40">
-        <v>6.89078092</v>
+        <v>7.072117260000001</v>
       </c>
       <c r="N40">
-        <v>7.93921908</v>
+        <v>7.757882739999999</v>
       </c>
       <c r="O40">
-        <v>1.98480477</v>
+        <v>1.939470685</v>
       </c>
       <c r="P40">
-        <v>5.95441431</v>
+        <v>5.818412055</v>
       </c>
       <c r="Q40">
-        <v>9.124414309999999</v>
+        <v>8.988412055</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1058101121518195</v>
+        <v>0.10662539308858</v>
       </c>
       <c r="T40">
-        <v>1.202822283166662</v>
+        <v>1.219163497049009</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.152150847947724</v>
+        <v>2.096967492872142</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08721298978403383</v>
+        <v>0.08722071003393955</v>
       </c>
       <c r="C41">
-        <v>143.0494548932139</v>
+        <v>140.6139339483113</v>
       </c>
       <c r="D41">
-        <v>231.8891548932139</v>
+        <v>231.8459339483113</v>
       </c>
       <c r="E41">
-        <v>88.7697</v>
+        <v>91.16200000000001</v>
       </c>
       <c r="F41">
-        <v>93.2997</v>
+        <v>95.69200000000001</v>
       </c>
       <c r="G41">
         <v>4.46</v>
@@ -4637,28 +4637,28 @@
         <v>14.83</v>
       </c>
       <c r="M41">
-        <v>7.072117260000001</v>
+        <v>7.253453600000001</v>
       </c>
       <c r="N41">
-        <v>7.757882739999999</v>
+        <v>7.576546399999999</v>
       </c>
       <c r="O41">
-        <v>1.939470685</v>
+        <v>1.8941366</v>
       </c>
       <c r="P41">
-        <v>5.818412055</v>
+        <v>5.682409799999999</v>
       </c>
       <c r="Q41">
-        <v>8.988412055</v>
+        <v>8.8524098</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.10662539308858</v>
+        <v>0.1074678500565659</v>
       </c>
       <c r="T41">
-        <v>1.219163497049009</v>
+        <v>1.236049418060768</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.096967492872142</v>
+        <v>2.044543305550338</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08722071003393955</v>
+        <v>0.09159493028384529</v>
       </c>
       <c r="C42">
-        <v>140.6139339483113</v>
+        <v>116.076274781933</v>
       </c>
       <c r="D42">
-        <v>231.8459339483113</v>
+        <v>209.700574781933</v>
       </c>
       <c r="E42">
-        <v>91.16200000000001</v>
+        <v>93.5543</v>
       </c>
       <c r="F42">
-        <v>95.69200000000001</v>
+        <v>98.0843</v>
       </c>
       <c r="G42">
         <v>4.46</v>
@@ -4719,45 +4719,45 @@
         <v>14.83</v>
       </c>
       <c r="M42">
-        <v>7.253453600000001</v>
+        <v>8.827586999999999</v>
       </c>
       <c r="N42">
-        <v>7.576546399999999</v>
+        <v>6.002413000000001</v>
       </c>
       <c r="O42">
-        <v>1.8941366</v>
+        <v>1.50060325</v>
       </c>
       <c r="P42">
-        <v>5.682409799999999</v>
+        <v>4.50180975</v>
       </c>
       <c r="Q42">
-        <v>8.8524098</v>
+        <v>7.67180975</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1074678500565659</v>
+        <v>0.1083388648878734</v>
       </c>
       <c r="T42">
-        <v>1.236049418060768</v>
+        <v>1.253507743174621</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.25</v>
       </c>
       <c r="W42">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.044543305550338</v>
+        <v>1.679960786566023</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09159493028384529</v>
+        <v>0.09170915053375099</v>
       </c>
       <c r="C43">
-        <v>116.076274781933</v>
+        <v>113.1622475929414</v>
       </c>
       <c r="D43">
-        <v>209.700574781933</v>
+        <v>209.1788475929414</v>
       </c>
       <c r="E43">
-        <v>93.5543</v>
+        <v>95.9466</v>
       </c>
       <c r="F43">
-        <v>98.0843</v>
+        <v>100.4766</v>
       </c>
       <c r="G43">
         <v>4.46</v>
@@ -4801,28 +4801,28 @@
         <v>14.83</v>
       </c>
       <c r="M43">
-        <v>8.827586999999999</v>
+        <v>9.042894</v>
       </c>
       <c r="N43">
-        <v>6.002413000000001</v>
+        <v>5.787106</v>
       </c>
       <c r="O43">
-        <v>1.50060325</v>
+        <v>1.4467765</v>
       </c>
       <c r="P43">
-        <v>4.50180975</v>
+        <v>4.340329499999999</v>
       </c>
       <c r="Q43">
-        <v>7.67180975</v>
+        <v>7.510329499999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1083388648878734</v>
+        <v>0.1092399147133638</v>
       </c>
       <c r="T43">
-        <v>1.253507743174621</v>
+        <v>1.271568079499296</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.679960786566023</v>
+        <v>1.639961720219213</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.091709150533751</v>
+        <v>0.09182337078365671</v>
       </c>
       <c r="C44">
-        <v>113.1622475929414</v>
+        <v>110.2508100365167</v>
       </c>
       <c r="D44">
-        <v>209.1788475929413</v>
+        <v>208.6597100365167</v>
       </c>
       <c r="E44">
-        <v>95.94659999999999</v>
+        <v>98.3389</v>
       </c>
       <c r="F44">
-        <v>100.4766</v>
+        <v>102.8689</v>
       </c>
       <c r="G44">
         <v>4.46</v>
@@ -4883,28 +4883,28 @@
         <v>14.83</v>
       </c>
       <c r="M44">
-        <v>9.042893999999999</v>
+        <v>9.258201</v>
       </c>
       <c r="N44">
-        <v>5.787106000000001</v>
+        <v>5.571799</v>
       </c>
       <c r="O44">
-        <v>1.4467765</v>
+        <v>1.39294975</v>
       </c>
       <c r="P44">
-        <v>4.340329500000001</v>
+        <v>4.178849250000001</v>
       </c>
       <c r="Q44">
-        <v>7.510329500000001</v>
+        <v>7.348849250000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1092399147133638</v>
+        <v>0.1101725803222048</v>
       </c>
       <c r="T44">
-        <v>1.271568079499296</v>
+        <v>1.290262111835363</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.639961720219213</v>
+        <v>1.601823075562952</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09182337078365671</v>
+        <v>0.09193759103356244</v>
       </c>
       <c r="C45">
-        <v>110.2508100365167</v>
+        <v>107.3419428796339</v>
       </c>
       <c r="D45">
-        <v>208.6597100365167</v>
+        <v>208.1431428796339</v>
       </c>
       <c r="E45">
-        <v>98.3389</v>
+        <v>100.7312</v>
       </c>
       <c r="F45">
-        <v>102.8689</v>
+        <v>105.2612</v>
       </c>
       <c r="G45">
         <v>4.46</v>
@@ -4965,28 +4965,28 @@
         <v>14.83</v>
       </c>
       <c r="M45">
-        <v>9.258201</v>
+        <v>9.473508000000001</v>
       </c>
       <c r="N45">
-        <v>5.571799</v>
+        <v>5.356491999999999</v>
       </c>
       <c r="O45">
-        <v>1.39294975</v>
+        <v>1.339123</v>
       </c>
       <c r="P45">
-        <v>4.178849250000001</v>
+        <v>4.017369</v>
       </c>
       <c r="Q45">
-        <v>7.348849250000001</v>
+        <v>7.187368999999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1101725803222048</v>
+        <v>0.1111385554170758</v>
       </c>
       <c r="T45">
-        <v>1.290262111835363</v>
+        <v>1.309623788183433</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.601823075562952</v>
+        <v>1.565418005663794</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09193759103356244</v>
+        <v>0.09205181128346816</v>
       </c>
       <c r="C46">
-        <v>107.3419428796339</v>
+        <v>104.4356270792544</v>
       </c>
       <c r="D46">
-        <v>208.1431428796339</v>
+        <v>207.6291270792544</v>
       </c>
       <c r="E46">
-        <v>100.7312</v>
+        <v>103.1235</v>
       </c>
       <c r="F46">
-        <v>105.2612</v>
+        <v>107.6535</v>
       </c>
       <c r="G46">
         <v>4.46</v>
@@ -5047,28 +5047,28 @@
         <v>14.83</v>
       </c>
       <c r="M46">
-        <v>9.473508000000001</v>
+        <v>9.688815</v>
       </c>
       <c r="N46">
-        <v>5.356491999999999</v>
+        <v>5.141185</v>
       </c>
       <c r="O46">
-        <v>1.339123</v>
+        <v>1.28529625</v>
       </c>
       <c r="P46">
-        <v>4.017369</v>
+        <v>3.85588875</v>
       </c>
       <c r="Q46">
-        <v>7.187368999999999</v>
+        <v>7.02588875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1111385554170758</v>
+        <v>0.112139656879033</v>
       </c>
       <c r="T46">
-        <v>1.309623788183433</v>
+        <v>1.329689525489614</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.565418005663794</v>
+        <v>1.530630938871266</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09205181128346816</v>
+        <v>0.1135340890649891</v>
       </c>
       <c r="C47">
-        <v>104.4356270792544</v>
+        <v>36.19248823248601</v>
       </c>
       <c r="D47">
-        <v>207.6291270792544</v>
+        <v>141.778288232486</v>
       </c>
       <c r="E47">
-        <v>103.1235</v>
+        <v>105.5158</v>
       </c>
       <c r="F47">
-        <v>107.6535</v>
+        <v>110.0458</v>
       </c>
       <c r="G47">
         <v>4.46</v>
@@ -5129,45 +5129,45 @@
         <v>14.83</v>
       </c>
       <c r="M47">
-        <v>9.688815</v>
+        <v>16.15472344</v>
       </c>
       <c r="N47">
-        <v>5.141185</v>
+        <v>-1.324723440000001</v>
       </c>
       <c r="O47">
-        <v>1.28529625</v>
+        <v>-0.3311808600000004</v>
       </c>
       <c r="P47">
-        <v>3.85588875</v>
+        <v>-0.9935425800000011</v>
       </c>
       <c r="Q47">
-        <v>7.02588875</v>
+        <v>2.176457419999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.112139656879033</v>
+        <v>0.1138957913352975</v>
       </c>
       <c r="T47">
-        <v>1.329689525489614</v>
+        <v>1.364888887405282</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.25</v>
+        <v>0.2294994410625453</v>
       </c>
       <c r="W47">
-        <v>0.0675</v>
+        <v>0.1131094820520184</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.530630938871266</v>
+        <v>0.9179977642501813</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1135340890649891</v>
+        <v>0.1145440890649891</v>
       </c>
       <c r="C48">
-        <v>36.19248823248601</v>
+        <v>31.71715719574568</v>
       </c>
       <c r="D48">
-        <v>141.778288232486</v>
+        <v>139.6952571957457</v>
       </c>
       <c r="E48">
-        <v>105.5158</v>
+        <v>107.9081</v>
       </c>
       <c r="F48">
-        <v>110.0458</v>
+        <v>112.4381</v>
       </c>
       <c r="G48">
         <v>4.46</v>
@@ -5211,37 +5211,37 @@
         <v>14.83</v>
       </c>
       <c r="M48">
-        <v>16.15472344</v>
+        <v>16.50591308</v>
       </c>
       <c r="N48">
-        <v>-1.324723440000001</v>
+        <v>-1.675913080000003</v>
       </c>
       <c r="O48">
-        <v>-0.3311808600000004</v>
+        <v>-0.4189782700000007</v>
       </c>
       <c r="P48">
-        <v>-0.9935425800000011</v>
+        <v>-1.256934810000002</v>
       </c>
       <c r="Q48">
-        <v>2.176457419999999</v>
+        <v>1.913065189999998</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1138957913352975</v>
+        <v>0.1151806175869069</v>
       </c>
       <c r="T48">
-        <v>1.364888887405282</v>
+        <v>1.390641507922363</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.2294994410625453</v>
+        <v>0.2246164742314273</v>
       </c>
       <c r="W48">
-        <v>0.1131094820520184</v>
+        <v>0.1138263015828265</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9179977642501813</v>
+        <v>0.8984658969257093</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1145440890649891</v>
+        <v>0.1155540890649891</v>
       </c>
       <c r="C49">
-        <v>31.71715719574568</v>
+        <v>27.30214839603295</v>
       </c>
       <c r="D49">
-        <v>139.6952571957457</v>
+        <v>137.6725483960329</v>
       </c>
       <c r="E49">
-        <v>107.9081</v>
+        <v>110.3004</v>
       </c>
       <c r="F49">
-        <v>112.4381</v>
+        <v>114.8304</v>
       </c>
       <c r="G49">
         <v>4.46</v>
@@ -5293,37 +5293,37 @@
         <v>14.83</v>
       </c>
       <c r="M49">
-        <v>16.50591308</v>
+        <v>16.85710272</v>
       </c>
       <c r="N49">
-        <v>-1.675913080000003</v>
+        <v>-2.02710272</v>
       </c>
       <c r="O49">
-        <v>-0.4189782700000007</v>
+        <v>-0.5067756800000001</v>
       </c>
       <c r="P49">
-        <v>-1.256934810000002</v>
+        <v>-1.52032704</v>
       </c>
       <c r="Q49">
-        <v>1.913065189999998</v>
+        <v>1.64967296</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1151806175869069</v>
+        <v>0.1165148602328089</v>
       </c>
       <c r="T49">
-        <v>1.390641507922363</v>
+        <v>1.417384613843947</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.2246164742314273</v>
+        <v>0.219936964351606</v>
       </c>
       <c r="W49">
-        <v>0.1138263015828265</v>
+        <v>0.1145132536331843</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8984658969257093</v>
+        <v>0.8797478574064239</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1155540890649891</v>
+        <v>0.1165640890649891</v>
       </c>
       <c r="C50">
-        <v>27.30214839603295</v>
+        <v>22.94487893599667</v>
       </c>
       <c r="D50">
-        <v>137.6725483960329</v>
+        <v>135.7075789359967</v>
       </c>
       <c r="E50">
-        <v>110.3004</v>
+        <v>112.6927</v>
       </c>
       <c r="F50">
-        <v>114.8304</v>
+        <v>117.2227</v>
       </c>
       <c r="G50">
         <v>4.46</v>
@@ -5375,37 +5375,37 @@
         <v>14.83</v>
       </c>
       <c r="M50">
-        <v>16.85710272</v>
+        <v>17.20829236</v>
       </c>
       <c r="N50">
-        <v>-2.02710272</v>
+        <v>-2.378292360000001</v>
       </c>
       <c r="O50">
-        <v>-0.5067756800000001</v>
+        <v>-0.5945730900000004</v>
       </c>
       <c r="P50">
-        <v>-1.52032704</v>
+        <v>-1.783719270000001</v>
       </c>
       <c r="Q50">
-        <v>1.64967296</v>
+        <v>1.386280729999999</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1165148602328089</v>
+        <v>0.1179014261197268</v>
       </c>
       <c r="T50">
-        <v>1.417384613843947</v>
+        <v>1.445176469017357</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.219936964351606</v>
+        <v>0.2154484548750425</v>
       </c>
       <c r="W50">
-        <v>0.1145132536331843</v>
+        <v>0.1151721668243438</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8797478574064239</v>
+        <v>0.8617938195001702</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1165640890649891</v>
+        <v>0.1175740890649891</v>
       </c>
       <c r="C51">
-        <v>22.94487893599667</v>
+        <v>18.64291130369485</v>
       </c>
       <c r="D51">
-        <v>135.7075789359967</v>
+        <v>133.7979113036948</v>
       </c>
       <c r="E51">
-        <v>112.6927</v>
+        <v>115.085</v>
       </c>
       <c r="F51">
-        <v>117.2227</v>
+        <v>119.615</v>
       </c>
       <c r="G51">
         <v>4.46</v>
@@ -5457,37 +5457,37 @@
         <v>14.83</v>
       </c>
       <c r="M51">
-        <v>17.20829236</v>
+        <v>17.559482</v>
       </c>
       <c r="N51">
-        <v>-2.378292360000001</v>
+        <v>-2.729481999999999</v>
       </c>
       <c r="O51">
-        <v>-0.5945730900000004</v>
+        <v>-0.6823704999999998</v>
       </c>
       <c r="P51">
-        <v>-1.783719270000001</v>
+        <v>-2.047111499999999</v>
       </c>
       <c r="Q51">
-        <v>1.386280729999999</v>
+        <v>1.122888500000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1179014261197268</v>
+        <v>0.1193434546421213</v>
       </c>
       <c r="T51">
-        <v>1.445176469017357</v>
+        <v>1.474079998397704</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2154484548750425</v>
+        <v>0.2111394857775417</v>
       </c>
       <c r="W51">
-        <v>0.1151721668243438</v>
+        <v>0.1158047234878569</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8617938195001702</v>
+        <v>0.844557943110167</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1175740890649891</v>
+        <v>0.1185840890649891</v>
       </c>
       <c r="C52">
-        <v>18.64291130369485</v>
+        <v>14.39394328527574</v>
       </c>
       <c r="D52">
-        <v>133.7979113036948</v>
+        <v>131.9412432852757</v>
       </c>
       <c r="E52">
-        <v>115.085</v>
+        <v>117.4773</v>
       </c>
       <c r="F52">
-        <v>119.615</v>
+        <v>122.0073</v>
       </c>
       <c r="G52">
         <v>4.46</v>
@@ -5539,37 +5539,37 @@
         <v>14.83</v>
       </c>
       <c r="M52">
-        <v>17.559482</v>
+        <v>17.91067164</v>
       </c>
       <c r="N52">
-        <v>-2.729481999999999</v>
+        <v>-3.08067164</v>
       </c>
       <c r="O52">
-        <v>-0.6823704999999998</v>
+        <v>-0.7701679100000001</v>
       </c>
       <c r="P52">
-        <v>-2.047111499999999</v>
+        <v>-2.31050373</v>
       </c>
       <c r="Q52">
-        <v>1.122888500000001</v>
+        <v>0.8594962699999997</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1193434546421213</v>
+        <v>0.1208443414715523</v>
       </c>
       <c r="T52">
-        <v>1.474079998397704</v>
+        <v>1.504163263671127</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2111394857775417</v>
+        <v>0.206999495860335</v>
       </c>
       <c r="W52">
-        <v>0.1158047234878569</v>
+        <v>0.1164124740077028</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.844557943110167</v>
+        <v>0.8279979834413401</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1185840890649891</v>
+        <v>0.1195940890649891</v>
       </c>
       <c r="C53">
-        <v>14.39394328527574</v>
+        <v>10.19579870603357</v>
       </c>
       <c r="D53">
-        <v>131.9412432852757</v>
+        <v>130.1353987060336</v>
       </c>
       <c r="E53">
-        <v>117.4773</v>
+        <v>119.8696</v>
       </c>
       <c r="F53">
-        <v>122.0073</v>
+        <v>124.3996</v>
       </c>
       <c r="G53">
         <v>4.46</v>
@@ -5621,37 +5621,37 @@
         <v>14.83</v>
       </c>
       <c r="M53">
-        <v>17.91067164</v>
+        <v>18.26186128</v>
       </c>
       <c r="N53">
-        <v>-3.08067164</v>
+        <v>-3.431861280000001</v>
       </c>
       <c r="O53">
-        <v>-0.7701679100000001</v>
+        <v>-0.8579653200000004</v>
       </c>
       <c r="P53">
-        <v>-2.31050373</v>
+        <v>-2.573895960000001</v>
       </c>
       <c r="Q53">
-        <v>0.8594962699999997</v>
+        <v>0.5961040399999988</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1208443414715523</v>
+        <v>0.1224077652522097</v>
       </c>
       <c r="T53">
-        <v>1.504163263671127</v>
+        <v>1.535499998330942</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.206999495860335</v>
+        <v>0.2030187363245593</v>
       </c>
       <c r="W53">
-        <v>0.1164124740077028</v>
+        <v>0.1169968495075547</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8279979834413401</v>
+        <v>0.8120749452982373</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1195940890649891</v>
+        <v>0.1503912669867974</v>
       </c>
       <c r="C54">
-        <v>10.19579870603357</v>
+        <v>-30.51521702748065</v>
       </c>
       <c r="D54">
-        <v>130.1353987060336</v>
+        <v>91.81668297251936</v>
       </c>
       <c r="E54">
-        <v>119.8696</v>
+        <v>122.2619</v>
       </c>
       <c r="F54">
-        <v>124.3996</v>
+        <v>126.7919</v>
       </c>
       <c r="G54">
         <v>4.46</v>
@@ -5703,45 +5703,45 @@
         <v>14.83</v>
       </c>
       <c r="M54">
-        <v>18.26186128</v>
+        <v>25.45981352</v>
       </c>
       <c r="N54">
-        <v>-3.431861280000001</v>
+        <v>-10.62981352</v>
       </c>
       <c r="O54">
-        <v>-0.8579653200000004</v>
+        <v>-2.65745338</v>
       </c>
       <c r="P54">
-        <v>-2.573895960000001</v>
+        <v>-7.972360140000001</v>
       </c>
       <c r="Q54">
-        <v>0.5961040399999988</v>
+        <v>-4.802360140000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1224077652522097</v>
+        <v>0.1265210749848275</v>
       </c>
       <c r="T54">
-        <v>1.535499998330942</v>
+        <v>1.617945779992574</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.2030187363245593</v>
+        <v>0.1456216478996426</v>
       </c>
       <c r="W54">
-        <v>0.1169968495075547</v>
+        <v>0.1715591731017518</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8120749452982373</v>
+        <v>0.5824865915985704</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1503912669867974</v>
+        <v>0.1519412669867974</v>
       </c>
       <c r="C55">
-        <v>-30.51521702748065</v>
+        <v>-34.24833255237075</v>
       </c>
       <c r="D55">
-        <v>91.81668297251936</v>
+        <v>90.47586744762926</v>
       </c>
       <c r="E55">
-        <v>122.2619</v>
+        <v>124.6542</v>
       </c>
       <c r="F55">
-        <v>126.7919</v>
+        <v>129.1842</v>
       </c>
       <c r="G55">
         <v>4.46</v>
@@ -5785,37 +5785,37 @@
         <v>14.83</v>
       </c>
       <c r="M55">
-        <v>25.45981352</v>
+        <v>25.94018736</v>
       </c>
       <c r="N55">
-        <v>-10.62981352</v>
+        <v>-11.11018736</v>
       </c>
       <c r="O55">
-        <v>-2.65745338</v>
+        <v>-2.777546840000001</v>
       </c>
       <c r="P55">
-        <v>-7.972360140000001</v>
+        <v>-8.332640520000002</v>
       </c>
       <c r="Q55">
-        <v>-4.802360140000001</v>
+        <v>-5.162640520000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1265210749848275</v>
+        <v>0.1282758809627585</v>
       </c>
       <c r="T55">
-        <v>1.617945779992574</v>
+        <v>1.653118514340239</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1456216478996426</v>
+        <v>0.1429249507163159</v>
       </c>
       <c r="W55">
-        <v>0.1715591731017518</v>
+        <v>0.1721006698961638</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5824865915985704</v>
+        <v>0.5716998028652635</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1519412669867974</v>
+        <v>0.1534912669867974</v>
       </c>
       <c r="C56">
-        <v>-34.24833255237075</v>
+        <v>-37.9428513716648</v>
       </c>
       <c r="D56">
-        <v>90.47586744762926</v>
+        <v>89.17364862833521</v>
       </c>
       <c r="E56">
-        <v>124.6542</v>
+        <v>127.0465</v>
       </c>
       <c r="F56">
-        <v>129.1842</v>
+        <v>131.5765</v>
       </c>
       <c r="G56">
         <v>4.46</v>
@@ -5867,37 +5867,37 @@
         <v>14.83</v>
       </c>
       <c r="M56">
-        <v>25.94018736</v>
+        <v>26.4205612</v>
       </c>
       <c r="N56">
-        <v>-11.11018736</v>
+        <v>-11.5905612</v>
       </c>
       <c r="O56">
-        <v>-2.777546840000001</v>
+        <v>-2.8976403</v>
       </c>
       <c r="P56">
-        <v>-8.332640520000002</v>
+        <v>-8.692920900000001</v>
       </c>
       <c r="Q56">
-        <v>-5.162640520000002</v>
+        <v>-5.522920900000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1282758809627585</v>
+        <v>0.1301086783174865</v>
       </c>
       <c r="T56">
-        <v>1.653118514340239</v>
+        <v>1.689854481325577</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1429249507163159</v>
+        <v>0.1403263152487465</v>
       </c>
       <c r="W56">
-        <v>0.1721006698961638</v>
+        <v>0.1726224758980517</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5716998028652635</v>
+        <v>0.561305260994986</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1534912669867974</v>
+        <v>0.1550412669867973</v>
       </c>
       <c r="C57">
-        <v>-37.9428513716648</v>
+        <v>-41.60041640553361</v>
       </c>
       <c r="D57">
-        <v>89.17364862833521</v>
+        <v>87.90838359446641</v>
       </c>
       <c r="E57">
-        <v>127.0465</v>
+        <v>129.4388</v>
       </c>
       <c r="F57">
-        <v>131.5765</v>
+        <v>133.9688</v>
       </c>
       <c r="G57">
         <v>4.46</v>
@@ -5949,37 +5949,37 @@
         <v>14.83</v>
       </c>
       <c r="M57">
-        <v>26.4205612</v>
+        <v>26.90093504</v>
       </c>
       <c r="N57">
-        <v>-11.5905612</v>
+        <v>-12.07093504</v>
       </c>
       <c r="O57">
-        <v>-2.8976403</v>
+        <v>-3.017733760000001</v>
       </c>
       <c r="P57">
-        <v>-8.692920900000001</v>
+        <v>-9.053201280000003</v>
       </c>
       <c r="Q57">
-        <v>-5.522920900000001</v>
+        <v>-5.883201280000003</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1301086783174865</v>
+        <v>0.1320247846428839</v>
       </c>
       <c r="T57">
-        <v>1.689854481325577</v>
+        <v>1.728260264992068</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1403263152487465</v>
+        <v>0.1378204881907331</v>
       </c>
       <c r="W57">
-        <v>0.1726224758980517</v>
+        <v>0.1731256459713008</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.561305260994986</v>
+        <v>0.5512819527629326</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1550412669867973</v>
+        <v>0.1565912669867973</v>
       </c>
       <c r="C58">
-        <v>-41.60041640553361</v>
+        <v>-45.22257863454537</v>
       </c>
       <c r="D58">
-        <v>87.90838359446641</v>
+        <v>86.67852136545466</v>
       </c>
       <c r="E58">
-        <v>129.4388</v>
+        <v>131.8311</v>
       </c>
       <c r="F58">
-        <v>133.9688</v>
+        <v>136.3611</v>
       </c>
       <c r="G58">
         <v>4.46</v>
@@ -6031,37 +6031,37 @@
         <v>14.83</v>
       </c>
       <c r="M58">
-        <v>26.90093504</v>
+        <v>27.38130888000001</v>
       </c>
       <c r="N58">
-        <v>-12.07093504</v>
+        <v>-12.55130888000001</v>
       </c>
       <c r="O58">
-        <v>-3.017733760000001</v>
+        <v>-3.137827220000001</v>
       </c>
       <c r="P58">
-        <v>-9.053201280000003</v>
+        <v>-9.413481660000004</v>
       </c>
       <c r="Q58">
-        <v>-5.883201280000003</v>
+        <v>-6.243481660000004</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1320247846428839</v>
+        <v>0.1340300121927184</v>
       </c>
       <c r="T58">
-        <v>1.728260264992068</v>
+        <v>1.76845236417793</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1378204881907331</v>
+        <v>0.1354025848891413</v>
       </c>
       <c r="W58">
-        <v>0.1731256459713008</v>
+        <v>0.1736111609542604</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5512819527629326</v>
+        <v>0.5416103395565652</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1565912669867973</v>
+        <v>0.1581412669867973</v>
       </c>
       <c r="C59">
-        <v>-45.22257863454537</v>
+        <v>-48.81080344223197</v>
       </c>
       <c r="D59">
-        <v>86.67852136545466</v>
+        <v>85.48259655776803</v>
       </c>
       <c r="E59">
-        <v>131.8311</v>
+        <v>134.2234</v>
       </c>
       <c r="F59">
-        <v>136.3611</v>
+        <v>138.7534</v>
       </c>
       <c r="G59">
         <v>4.46</v>
@@ -6113,37 +6113,37 @@
         <v>14.83</v>
       </c>
       <c r="M59">
-        <v>27.38130888000001</v>
+        <v>27.86168272</v>
       </c>
       <c r="N59">
-        <v>-12.55130888000001</v>
+        <v>-13.03168272</v>
       </c>
       <c r="O59">
-        <v>-3.137827220000001</v>
+        <v>-3.25792068</v>
       </c>
       <c r="P59">
-        <v>-9.413481660000004</v>
+        <v>-9.773762040000001</v>
       </c>
       <c r="Q59">
-        <v>-6.243481660000004</v>
+        <v>-6.603762040000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1340300121927184</v>
+        <v>0.1361307267687355</v>
       </c>
       <c r="T59">
-        <v>1.76845236417793</v>
+        <v>1.810558372848833</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1354025848891413</v>
+        <v>0.1330680575634665</v>
       </c>
       <c r="W59">
-        <v>0.1736111609542604</v>
+        <v>0.1740799340412559</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5416103395565652</v>
+        <v>0.5322722302538661</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1581412669867974</v>
+        <v>0.1596912669867973</v>
       </c>
       <c r="C60">
-        <v>-48.81080344223197</v>
+        <v>-52.36647643974104</v>
       </c>
       <c r="D60">
-        <v>85.48259655776801</v>
+        <v>84.31922356025895</v>
       </c>
       <c r="E60">
-        <v>134.2234</v>
+        <v>136.6157</v>
       </c>
       <c r="F60">
-        <v>138.7534</v>
+        <v>141.1457</v>
       </c>
       <c r="G60">
         <v>4.46</v>
@@ -6195,37 +6195,37 @@
         <v>14.83</v>
       </c>
       <c r="M60">
-        <v>27.86168271999999</v>
+        <v>28.34205656</v>
       </c>
       <c r="N60">
-        <v>-13.03168271999999</v>
+        <v>-13.51205656</v>
       </c>
       <c r="O60">
-        <v>-3.257920679999998</v>
+        <v>-3.378014139999999</v>
       </c>
       <c r="P60">
-        <v>-9.773762039999996</v>
+        <v>-10.13404242</v>
       </c>
       <c r="Q60">
-        <v>-6.603762039999996</v>
+        <v>-6.964042419999997</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1361307267687355</v>
+        <v>0.1383339152265095</v>
       </c>
       <c r="T60">
-        <v>1.810558372848833</v>
+        <v>1.854718333162219</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1330680575634665</v>
+        <v>0.1308126667573061</v>
       </c>
       <c r="W60">
-        <v>0.1740799340412559</v>
+        <v>0.1745328165151329</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5322722302538661</v>
+        <v>0.5232506670292243</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1596912669867973</v>
+        <v>0.1612412669867973</v>
       </c>
       <c r="C61">
-        <v>-52.36647643974104</v>
+        <v>-55.89090882125198</v>
       </c>
       <c r="D61">
-        <v>84.31922356025895</v>
+        <v>83.18709117874801</v>
       </c>
       <c r="E61">
-        <v>136.6157</v>
+        <v>139.008</v>
       </c>
       <c r="F61">
-        <v>141.1457</v>
+        <v>143.538</v>
       </c>
       <c r="G61">
         <v>4.46</v>
@@ -6277,37 +6277,37 @@
         <v>14.83</v>
       </c>
       <c r="M61">
-        <v>28.34205656</v>
+        <v>28.8224304</v>
       </c>
       <c r="N61">
-        <v>-13.51205656</v>
+        <v>-13.9924304</v>
       </c>
       <c r="O61">
-        <v>-3.378014139999999</v>
+        <v>-3.4981076</v>
       </c>
       <c r="P61">
-        <v>-10.13404242</v>
+        <v>-10.4943228</v>
       </c>
       <c r="Q61">
-        <v>-6.964042419999997</v>
+        <v>-7.324322799999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1383339152265095</v>
+        <v>0.1406472631071723</v>
       </c>
       <c r="T61">
-        <v>1.854718333162219</v>
+        <v>1.901086291491275</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1308126667573061</v>
+        <v>0.1286324556446843</v>
       </c>
       <c r="W61">
-        <v>0.1745328165151329</v>
+        <v>0.1749706029065474</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5232506670292243</v>
+        <v>0.5145298225787371</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1612412669867973</v>
+        <v>0.1627912669867974</v>
       </c>
       <c r="C62">
-        <v>-55.89090882125198</v>
+        <v>-59.38534229367272</v>
       </c>
       <c r="D62">
-        <v>83.18709117874801</v>
+        <v>82.08495770632727</v>
       </c>
       <c r="E62">
-        <v>139.008</v>
+        <v>141.4003</v>
       </c>
       <c r="F62">
-        <v>143.538</v>
+        <v>145.9303</v>
       </c>
       <c r="G62">
         <v>4.46</v>
@@ -6359,37 +6359,37 @@
         <v>14.83</v>
       </c>
       <c r="M62">
-        <v>28.8224304</v>
+        <v>29.30280424</v>
       </c>
       <c r="N62">
-        <v>-13.9924304</v>
+        <v>-14.47280424</v>
       </c>
       <c r="O62">
-        <v>-3.4981076</v>
+        <v>-3.618201059999999</v>
       </c>
       <c r="P62">
-        <v>-10.4943228</v>
+        <v>-10.85460318</v>
       </c>
       <c r="Q62">
-        <v>-7.324322799999999</v>
+        <v>-7.684603179999998</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1406472631071723</v>
+        <v>0.1430792442124844</v>
       </c>
       <c r="T62">
-        <v>1.901086291491275</v>
+        <v>1.949832093837205</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1286324556446843</v>
+        <v>0.1265237268636239</v>
       </c>
       <c r="W62">
-        <v>0.1749706029065474</v>
+        <v>0.1753940356457843</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5145298225787371</v>
+        <v>0.5060949074544956</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1627912669867974</v>
+        <v>0.1865122373761929</v>
       </c>
       <c r="C63">
-        <v>-59.38534229367272</v>
+        <v>-75.61535028179125</v>
       </c>
       <c r="D63">
-        <v>82.08495770632727</v>
+        <v>68.24724971820875</v>
       </c>
       <c r="E63">
-        <v>141.4003</v>
+        <v>143.7926</v>
       </c>
       <c r="F63">
-        <v>145.9303</v>
+        <v>148.3226</v>
       </c>
       <c r="G63">
         <v>4.46</v>
@@ -6441,45 +6441,45 @@
         <v>14.83</v>
       </c>
       <c r="M63">
-        <v>29.30280424</v>
+        <v>34.97446908</v>
       </c>
       <c r="N63">
-        <v>-14.47280424</v>
+        <v>-20.14446908</v>
       </c>
       <c r="O63">
-        <v>-3.618201059999999</v>
+        <v>-5.03611727</v>
       </c>
       <c r="P63">
-        <v>-10.85460318</v>
+        <v>-15.10835181</v>
       </c>
       <c r="Q63">
-        <v>-7.684603179999998</v>
+        <v>-11.93835181</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1430792442124844</v>
+        <v>0.1468786200849063</v>
       </c>
       <c r="T63">
-        <v>1.949832093837205</v>
+        <v>2.025985491949732</v>
       </c>
       <c r="U63">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.1265237268636239</v>
+        <v>0.1060058979457137</v>
       </c>
       <c r="W63">
-        <v>0.1753940356457843</v>
+        <v>0.2108038092644007</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5060949074544956</v>
+        <v>0.4240235917828549</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1865122373761929</v>
+        <v>0.1884122373761929</v>
       </c>
       <c r="C64">
-        <v>-75.61535028179125</v>
+        <v>-78.91689746036641</v>
       </c>
       <c r="D64">
-        <v>68.24724971820875</v>
+        <v>67.33800253963359</v>
       </c>
       <c r="E64">
-        <v>143.7926</v>
+        <v>146.1849</v>
       </c>
       <c r="F64">
-        <v>148.3226</v>
+        <v>150.7149</v>
       </c>
       <c r="G64">
         <v>4.46</v>
@@ -6523,37 +6523,37 @@
         <v>14.83</v>
       </c>
       <c r="M64">
-        <v>34.97446908</v>
+        <v>35.53857342</v>
       </c>
       <c r="N64">
-        <v>-20.14446908</v>
+        <v>-20.70857342</v>
       </c>
       <c r="O64">
-        <v>-5.03611727</v>
+        <v>-5.177143355</v>
       </c>
       <c r="P64">
-        <v>-15.10835181</v>
+        <v>-15.531430065</v>
       </c>
       <c r="Q64">
-        <v>-11.93835181</v>
+        <v>-12.361430065</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1468786200849063</v>
+        <v>0.1496104746817957</v>
       </c>
       <c r="T64">
-        <v>2.025985491949732</v>
+        <v>2.080741856597021</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1060058979457137</v>
+        <v>0.1043232646449881</v>
       </c>
       <c r="W64">
-        <v>0.2108038092644007</v>
+        <v>0.2112005741967118</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4240235917828549</v>
+        <v>0.4172930585799524</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1884122373761929</v>
+        <v>0.1903122373761929</v>
       </c>
       <c r="C65">
-        <v>-78.91689746036641</v>
+        <v>-82.19453566527046</v>
       </c>
       <c r="D65">
-        <v>67.33800253963359</v>
+        <v>66.45266433472955</v>
       </c>
       <c r="E65">
-        <v>146.1849</v>
+        <v>148.5772</v>
       </c>
       <c r="F65">
-        <v>150.7149</v>
+        <v>153.1072</v>
       </c>
       <c r="G65">
         <v>4.46</v>
@@ -6605,37 +6605,37 @@
         <v>14.83</v>
       </c>
       <c r="M65">
-        <v>35.53857342</v>
+        <v>36.10267776000001</v>
       </c>
       <c r="N65">
-        <v>-20.70857342</v>
+        <v>-21.27267776000001</v>
       </c>
       <c r="O65">
-        <v>-5.177143355</v>
+        <v>-5.318169440000002</v>
       </c>
       <c r="P65">
-        <v>-15.531430065</v>
+        <v>-15.95450832000001</v>
       </c>
       <c r="Q65">
-        <v>-12.361430065</v>
+        <v>-12.78450832000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1496104746817957</v>
+        <v>0.1524940989785123</v>
       </c>
       <c r="T65">
-        <v>2.080741856597021</v>
+        <v>2.138540241502495</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.1043232646449881</v>
+        <v>0.1026932136349101</v>
       </c>
       <c r="W65">
-        <v>0.2112005741967118</v>
+        <v>0.2115849402248882</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4172930585799524</v>
+        <v>0.4107728545396405</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1903122373761929</v>
+        <v>0.1922122373761929</v>
       </c>
       <c r="C66">
-        <v>-82.19453566527046</v>
+        <v>-85.44919570087031</v>
       </c>
       <c r="D66">
-        <v>66.45266433472955</v>
+        <v>65.59030429912971</v>
       </c>
       <c r="E66">
-        <v>148.5772</v>
+        <v>150.9695</v>
       </c>
       <c r="F66">
-        <v>153.1072</v>
+        <v>155.4995</v>
       </c>
       <c r="G66">
         <v>4.46</v>
@@ -6687,37 +6687,37 @@
         <v>14.83</v>
       </c>
       <c r="M66">
-        <v>36.10267776000001</v>
+        <v>36.66678210000001</v>
       </c>
       <c r="N66">
-        <v>-21.27267776000001</v>
+        <v>-21.83678210000001</v>
       </c>
       <c r="O66">
-        <v>-5.318169440000002</v>
+        <v>-5.459195525000002</v>
       </c>
       <c r="P66">
-        <v>-15.95450832000001</v>
+        <v>-16.37758657500001</v>
       </c>
       <c r="Q66">
-        <v>-12.78450832000001</v>
+        <v>-13.20758657500001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1524940989785123</v>
+        <v>0.1555425018064698</v>
       </c>
       <c r="T66">
-        <v>2.138540241502495</v>
+        <v>2.199641391259709</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.1026932136349101</v>
+        <v>0.1011133180405269</v>
       </c>
       <c r="W66">
-        <v>0.2115849402248882</v>
+        <v>0.2119574796060437</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.4107728545396405</v>
+        <v>0.4044532721621076</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1922122373761929</v>
+        <v>0.1941122373761929</v>
       </c>
       <c r="C67">
-        <v>-85.44919570087031</v>
+        <v>-88.68176067409865</v>
       </c>
       <c r="D67">
-        <v>65.59030429912971</v>
+        <v>64.75003932590134</v>
       </c>
       <c r="E67">
-        <v>150.9695</v>
+        <v>153.3618</v>
       </c>
       <c r="F67">
-        <v>155.4995</v>
+        <v>157.8918</v>
       </c>
       <c r="G67">
         <v>4.46</v>
@@ -6769,37 +6769,37 @@
         <v>14.83</v>
       </c>
       <c r="M67">
-        <v>36.66678210000001</v>
+        <v>37.23088644</v>
       </c>
       <c r="N67">
-        <v>-21.83678210000001</v>
+        <v>-22.40088644</v>
       </c>
       <c r="O67">
-        <v>-5.459195525000002</v>
+        <v>-5.60022161</v>
       </c>
       <c r="P67">
-        <v>-16.37758657500001</v>
+        <v>-16.80066483</v>
       </c>
       <c r="Q67">
-        <v>-13.20758657500001</v>
+        <v>-13.63066483</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1555425018064698</v>
+        <v>0.1587702224478365</v>
       </c>
       <c r="T67">
-        <v>2.199641391259709</v>
+        <v>2.264336726296759</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1011133180405269</v>
+        <v>0.09958129807021592</v>
       </c>
       <c r="W67">
-        <v>0.2119574796060437</v>
+        <v>0.2123187299150431</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.4044532721621076</v>
+        <v>0.3983251922808636</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1941122373761929</v>
+        <v>0.1960122373761929</v>
       </c>
       <c r="C68">
-        <v>-88.68176067409865</v>
+        <v>-91.89306901102336</v>
       </c>
       <c r="D68">
-        <v>64.75003932590134</v>
+        <v>63.93103098897664</v>
       </c>
       <c r="E68">
-        <v>153.3618</v>
+        <v>155.7541</v>
       </c>
       <c r="F68">
-        <v>157.8918</v>
+        <v>160.2841</v>
       </c>
       <c r="G68">
         <v>4.46</v>
@@ -6851,37 +6851,37 @@
         <v>14.83</v>
       </c>
       <c r="M68">
-        <v>37.23088644</v>
+        <v>37.79499078</v>
       </c>
       <c r="N68">
-        <v>-22.40088644</v>
+        <v>-22.96499078</v>
       </c>
       <c r="O68">
-        <v>-5.60022161</v>
+        <v>-5.741247695</v>
       </c>
       <c r="P68">
-        <v>-16.80066483</v>
+        <v>-17.223743085</v>
       </c>
       <c r="Q68">
-        <v>-13.63066483</v>
+        <v>-14.053743085</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1587702224478365</v>
+        <v>0.1621935625220134</v>
       </c>
       <c r="T68">
-        <v>2.264336726296759</v>
+        <v>2.332952990729994</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.09958129807021592</v>
+        <v>0.09809501003931717</v>
       </c>
       <c r="W68">
-        <v>0.2123187299150431</v>
+        <v>0.212669196632729</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3983251922808636</v>
+        <v>0.3923800401572687</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1960122373761929</v>
+        <v>0.1979122373761928</v>
       </c>
       <c r="C69">
-        <v>-91.89306901102336</v>
+        <v>-95.08391724734076</v>
       </c>
       <c r="D69">
-        <v>63.93103098897664</v>
+        <v>63.13248275265924</v>
       </c>
       <c r="E69">
-        <v>155.7541</v>
+        <v>158.1464</v>
       </c>
       <c r="F69">
-        <v>160.2841</v>
+        <v>162.6764</v>
       </c>
       <c r="G69">
         <v>4.46</v>
@@ -6933,37 +6933,37 @@
         <v>14.83</v>
       </c>
       <c r="M69">
-        <v>37.79499078</v>
+        <v>38.35909512</v>
       </c>
       <c r="N69">
-        <v>-22.96499078</v>
+        <v>-23.52909512</v>
       </c>
       <c r="O69">
-        <v>-5.741247695</v>
+        <v>-5.88227378</v>
       </c>
       <c r="P69">
-        <v>-17.223743085</v>
+        <v>-17.64682134</v>
       </c>
       <c r="Q69">
-        <v>-14.053743085</v>
+        <v>-14.47682134</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1621935625220134</v>
+        <v>0.1658308613508263</v>
       </c>
       <c r="T69">
-        <v>2.332952990729994</v>
+        <v>2.405857771690306</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.09809501003931717</v>
+        <v>0.09665243636226839</v>
       </c>
       <c r="W69">
-        <v>0.212669196632729</v>
+        <v>0.2130093555057771</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3923800401572687</v>
+        <v>0.3866097454490736</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1979122373761928</v>
+        <v>0.1998122373761929</v>
       </c>
       <c r="C70">
-        <v>-95.08391724734076</v>
+        <v>-98.25506261231692</v>
       </c>
       <c r="D70">
-        <v>63.13248275265924</v>
+        <v>62.35363738768309</v>
       </c>
       <c r="E70">
-        <v>158.1464</v>
+        <v>160.5387</v>
       </c>
       <c r="F70">
-        <v>162.6764</v>
+        <v>165.0687</v>
       </c>
       <c r="G70">
         <v>4.46</v>
@@ -7015,37 +7015,37 @@
         <v>14.83</v>
       </c>
       <c r="M70">
-        <v>38.35909512</v>
+        <v>38.92319946000001</v>
       </c>
       <c r="N70">
-        <v>-23.52909512</v>
+        <v>-24.09319946000001</v>
       </c>
       <c r="O70">
-        <v>-5.88227378</v>
+        <v>-6.023299865000002</v>
       </c>
       <c r="P70">
-        <v>-17.64682134</v>
+        <v>-18.06989959500001</v>
       </c>
       <c r="Q70">
-        <v>-14.47682134</v>
+        <v>-14.89989959500001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1658308613508263</v>
+        <v>0.1697028246202078</v>
       </c>
       <c r="T70">
-        <v>2.405857771690306</v>
+        <v>2.483466086906124</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.09665243636226839</v>
+        <v>0.09525167641498912</v>
       </c>
       <c r="W70">
-        <v>0.2130093555057771</v>
+        <v>0.2133396547013456</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3866097454490736</v>
+        <v>0.3810067056599564</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1998122373761929</v>
+        <v>0.2017122373761929</v>
       </c>
       <c r="C71">
-        <v>-98.25506261231692</v>
+        <v>-101.4072254237956</v>
       </c>
       <c r="D71">
-        <v>62.35363738768309</v>
+        <v>61.59377457620446</v>
       </c>
       <c r="E71">
-        <v>160.5387</v>
+        <v>162.931</v>
       </c>
       <c r="F71">
-        <v>165.0687</v>
+        <v>167.461</v>
       </c>
       <c r="G71">
         <v>4.46</v>
@@ -7097,37 +7097,37 @@
         <v>14.83</v>
       </c>
       <c r="M71">
-        <v>38.92319946000001</v>
+        <v>39.48730380000001</v>
       </c>
       <c r="N71">
-        <v>-24.09319946000001</v>
+        <v>-24.65730380000001</v>
       </c>
       <c r="O71">
-        <v>-6.023299865000002</v>
+        <v>-6.164325950000002</v>
       </c>
       <c r="P71">
-        <v>-18.06989959500001</v>
+        <v>-18.49297785000001</v>
       </c>
       <c r="Q71">
-        <v>-14.89989959500001</v>
+        <v>-15.32297785000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1697028246202078</v>
+        <v>0.1738329187742147</v>
       </c>
       <c r="T71">
-        <v>2.483466086906124</v>
+        <v>2.566248289802994</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.09525167641498912</v>
+        <v>0.09389093818048928</v>
       </c>
       <c r="W71">
-        <v>0.2133396547013456</v>
+        <v>0.2136605167770406</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3810067056599564</v>
+        <v>0.3755637527219571</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2017122373761929</v>
+        <v>0.2036122373761929</v>
       </c>
       <c r="C72">
-        <v>-101.4072254237956</v>
+        <v>-104.5410913101965</v>
       </c>
       <c r="D72">
-        <v>61.59377457620446</v>
+        <v>60.85220868980355</v>
       </c>
       <c r="E72">
-        <v>162.931</v>
+        <v>165.3233</v>
       </c>
       <c r="F72">
-        <v>167.461</v>
+        <v>169.8533</v>
       </c>
       <c r="G72">
         <v>4.46</v>
@@ -7179,37 +7179,37 @@
         <v>14.83</v>
       </c>
       <c r="M72">
-        <v>39.48730380000001</v>
+        <v>40.05140814000001</v>
       </c>
       <c r="N72">
-        <v>-24.65730380000001</v>
+        <v>-25.22140814000001</v>
       </c>
       <c r="O72">
-        <v>-6.164325950000002</v>
+        <v>-6.305352035000002</v>
       </c>
       <c r="P72">
-        <v>-18.49297785000001</v>
+        <v>-18.91605610500001</v>
       </c>
       <c r="Q72">
-        <v>-15.32297785000001</v>
+        <v>-15.74605610500001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1738329187742147</v>
+        <v>0.1782478470078084</v>
       </c>
       <c r="T72">
-        <v>2.566248289802994</v>
+        <v>2.654739610141029</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.09389093818048928</v>
+        <v>0.09256853060048238</v>
       </c>
       <c r="W72">
-        <v>0.2136605167770406</v>
+        <v>0.2139723404844062</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3755637527219571</v>
+        <v>0.3702741224019295</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2036122373761928</v>
+        <v>0.2055122373761928</v>
       </c>
       <c r="C73">
-        <v>-104.5410913101964</v>
+        <v>-107.657313273911</v>
       </c>
       <c r="D73">
-        <v>60.85220868980355</v>
+        <v>60.12828672608895</v>
       </c>
       <c r="E73">
-        <v>165.3233</v>
+        <v>167.7156</v>
       </c>
       <c r="F73">
-        <v>169.8533</v>
+        <v>172.2456</v>
       </c>
       <c r="G73">
         <v>4.46</v>
@@ -7261,37 +7261,37 @@
         <v>14.83</v>
       </c>
       <c r="M73">
-        <v>40.05140814</v>
+        <v>40.61551248</v>
       </c>
       <c r="N73">
-        <v>-25.22140814</v>
+        <v>-25.78551248</v>
       </c>
       <c r="O73">
-        <v>-6.305352035</v>
+        <v>-6.44637812</v>
       </c>
       <c r="P73">
-        <v>-18.916056105</v>
+        <v>-19.33913436</v>
       </c>
       <c r="Q73">
-        <v>-15.746056105</v>
+        <v>-16.16913436</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1782478470078083</v>
+        <v>0.1829781272580872</v>
       </c>
       <c r="T73">
-        <v>2.654739610141028</v>
+        <v>2.749551739074636</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09256853060048241</v>
+        <v>0.09128285656436459</v>
       </c>
       <c r="W73">
-        <v>0.2139723404844062</v>
+        <v>0.2142755024221228</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3702741224019296</v>
+        <v>0.3651314262574583</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2055122373761928</v>
+        <v>0.2074122373761929</v>
       </c>
       <c r="C74">
-        <v>-107.657313273911</v>
+        <v>-110.7565136091477</v>
       </c>
       <c r="D74">
-        <v>60.12828672608895</v>
+        <v>59.42138639085234</v>
       </c>
       <c r="E74">
-        <v>167.7156</v>
+        <v>170.1079</v>
       </c>
       <c r="F74">
-        <v>172.2456</v>
+        <v>174.6379</v>
       </c>
       <c r="G74">
         <v>4.46</v>
@@ -7343,37 +7343,37 @@
         <v>14.83</v>
       </c>
       <c r="M74">
-        <v>40.61551248</v>
+        <v>41.17961682</v>
       </c>
       <c r="N74">
-        <v>-25.78551248</v>
+        <v>-26.34961682</v>
       </c>
       <c r="O74">
-        <v>-6.44637812</v>
+        <v>-6.587404205</v>
       </c>
       <c r="P74">
-        <v>-19.33913436</v>
+        <v>-19.762212615</v>
       </c>
       <c r="Q74">
-        <v>-16.16913436</v>
+        <v>-16.592212615</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1829781272580872</v>
+        <v>0.1880587986380163</v>
       </c>
       <c r="T74">
-        <v>2.749551739074636</v>
+        <v>2.851386988669993</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09128285656436459</v>
+        <v>0.09003240647444179</v>
       </c>
       <c r="W74">
-        <v>0.2142755024221228</v>
+        <v>0.2145703585533267</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3651314262574583</v>
+        <v>0.3601296258977671</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2074122373761929</v>
+        <v>0.2093122373761929</v>
       </c>
       <c r="C75">
-        <v>-110.7565136091477</v>
+        <v>-113.8392856860655</v>
       </c>
       <c r="D75">
-        <v>59.42138639085234</v>
+        <v>58.73091431393451</v>
       </c>
       <c r="E75">
-        <v>170.1079</v>
+        <v>172.5002</v>
       </c>
       <c r="F75">
-        <v>174.6379</v>
+        <v>177.0302</v>
       </c>
       <c r="G75">
         <v>4.46</v>
@@ -7425,37 +7425,37 @@
         <v>14.83</v>
       </c>
       <c r="M75">
-        <v>41.17961682</v>
+        <v>41.74372116</v>
       </c>
       <c r="N75">
-        <v>-26.34961682</v>
+        <v>-26.91372116</v>
       </c>
       <c r="O75">
-        <v>-6.587404205</v>
+        <v>-6.72843029</v>
       </c>
       <c r="P75">
-        <v>-19.762212615</v>
+        <v>-20.18529087</v>
       </c>
       <c r="Q75">
-        <v>-16.592212615</v>
+        <v>-17.01529087</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1880587986380163</v>
+        <v>0.1935302908933247</v>
       </c>
       <c r="T75">
-        <v>2.851386988669993</v>
+        <v>2.961055719003454</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09003240647444179</v>
+        <v>0.08881575233289528</v>
       </c>
       <c r="W75">
-        <v>0.2145703585533267</v>
+        <v>0.2148572455999033</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3601296258977671</v>
+        <v>0.3552630093315811</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2093122373761929</v>
+        <v>0.2112122373761928</v>
       </c>
       <c r="C76">
-        <v>-113.8392856860655</v>
+        <v>-116.9061956119484</v>
       </c>
       <c r="D76">
-        <v>58.73091431393451</v>
+        <v>58.05630438805163</v>
       </c>
       <c r="E76">
-        <v>172.5002</v>
+        <v>174.8925</v>
       </c>
       <c r="F76">
-        <v>177.0302</v>
+        <v>179.4225</v>
       </c>
       <c r="G76">
         <v>4.46</v>
@@ -7507,37 +7507,37 @@
         <v>14.83</v>
       </c>
       <c r="M76">
-        <v>41.74372116</v>
+        <v>42.3078255</v>
       </c>
       <c r="N76">
-        <v>-26.91372116</v>
+        <v>-27.4778255</v>
       </c>
       <c r="O76">
-        <v>-6.72843029</v>
+        <v>-6.869456375</v>
       </c>
       <c r="P76">
-        <v>-20.18529087</v>
+        <v>-20.608369125</v>
       </c>
       <c r="Q76">
-        <v>-17.01529087</v>
+        <v>-17.438369125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1935302908933247</v>
+        <v>0.1994395025290576</v>
       </c>
       <c r="T76">
-        <v>2.961055719003454</v>
+        <v>3.079497947763592</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.08881575233289528</v>
+        <v>0.08763154230179</v>
       </c>
       <c r="W76">
-        <v>0.2148572455999033</v>
+        <v>0.2151364823252379</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3552630093315811</v>
+        <v>0.35052616920716</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2112122373761928</v>
+        <v>0.2131122373761929</v>
       </c>
       <c r="C77">
-        <v>-116.9061956119484</v>
+        <v>-119.9577837791927</v>
       </c>
       <c r="D77">
-        <v>58.05630438805163</v>
+        <v>57.39701622080731</v>
       </c>
       <c r="E77">
-        <v>174.8925</v>
+        <v>177.2848</v>
       </c>
       <c r="F77">
-        <v>179.4225</v>
+        <v>181.8148</v>
       </c>
       <c r="G77">
         <v>4.46</v>
@@ -7589,37 +7589,37 @@
         <v>14.83</v>
       </c>
       <c r="M77">
-        <v>42.3078255</v>
+        <v>42.87192984</v>
       </c>
       <c r="N77">
-        <v>-27.4778255</v>
+        <v>-28.04192984</v>
       </c>
       <c r="O77">
-        <v>-6.869456375</v>
+        <v>-7.01048246</v>
       </c>
       <c r="P77">
-        <v>-20.608369125</v>
+        <v>-21.03144738</v>
       </c>
       <c r="Q77">
-        <v>-17.438369125</v>
+        <v>-17.86144738</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1994395025290576</v>
+        <v>0.2058411484677684</v>
       </c>
       <c r="T77">
-        <v>3.079497947763592</v>
+        <v>3.207810362253742</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.08763154230179</v>
+        <v>0.08647849569255593</v>
       </c>
       <c r="W77">
-        <v>0.2151364823252379</v>
+        <v>0.2154083707156953</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.35052616920716</v>
+        <v>0.3459139827702237</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2131122373761929</v>
+        <v>0.2150122373761928</v>
       </c>
       <c r="C78">
-        <v>-119.9577837791927</v>
+        <v>-122.9945663090058</v>
       </c>
       <c r="D78">
-        <v>57.39701622080731</v>
+        <v>56.75253369099424</v>
       </c>
       <c r="E78">
-        <v>177.2848</v>
+        <v>179.6771</v>
       </c>
       <c r="F78">
-        <v>181.8148</v>
+        <v>184.2071</v>
       </c>
       <c r="G78">
         <v>4.46</v>
@@ -7671,37 +7671,37 @@
         <v>14.83</v>
       </c>
       <c r="M78">
-        <v>42.87192984</v>
+        <v>43.43603418</v>
       </c>
       <c r="N78">
-        <v>-28.04192984</v>
+        <v>-28.60603418</v>
       </c>
       <c r="O78">
-        <v>-7.01048246</v>
+        <v>-7.151508545</v>
       </c>
       <c r="P78">
-        <v>-21.03144738</v>
+        <v>-21.454525635</v>
       </c>
       <c r="Q78">
-        <v>-17.86144738</v>
+        <v>-18.284525635</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2058411484677684</v>
+        <v>0.2127994592707148</v>
       </c>
       <c r="T78">
-        <v>3.207810362253742</v>
+        <v>3.347280378003905</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.08647849569255593</v>
+        <v>0.08535539834589936</v>
       </c>
       <c r="W78">
-        <v>0.2154083707156953</v>
+        <v>0.2156731970700369</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3459139827702237</v>
+        <v>0.3414215933835973</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2150122373761928</v>
+        <v>0.2169122373761929</v>
       </c>
       <c r="C79">
-        <v>-122.9945663090058</v>
+        <v>-126.0170363989206</v>
       </c>
       <c r="D79">
-        <v>56.75253369099424</v>
+        <v>56.12236360107936</v>
       </c>
       <c r="E79">
-        <v>179.6771</v>
+        <v>182.0694</v>
       </c>
       <c r="F79">
-        <v>184.2071</v>
+        <v>186.5994</v>
       </c>
       <c r="G79">
         <v>4.46</v>
@@ -7753,37 +7753,37 @@
         <v>14.83</v>
       </c>
       <c r="M79">
-        <v>43.43603418</v>
+        <v>44.00013852</v>
       </c>
       <c r="N79">
-        <v>-28.60603418</v>
+        <v>-29.17013852</v>
       </c>
       <c r="O79">
-        <v>-7.151508545</v>
+        <v>-7.29253463</v>
       </c>
       <c r="P79">
-        <v>-21.454525635</v>
+        <v>-21.87760389</v>
       </c>
       <c r="Q79">
-        <v>-18.284525635</v>
+        <v>-18.70760389</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2127994592707148</v>
+        <v>0.2203903437830201</v>
       </c>
       <c r="T79">
-        <v>3.347280378003905</v>
+        <v>3.499429486094991</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.08535539834589936</v>
+        <v>0.08426109836710578</v>
       </c>
       <c r="W79">
-        <v>0.2156731970700369</v>
+        <v>0.2159312330050364</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3414215933835973</v>
+        <v>0.3370443934684231</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2169122373761929</v>
+        <v>0.2188122373761928</v>
       </c>
       <c r="C80">
-        <v>-126.0170363989206</v>
+        <v>-129.0256655815217</v>
       </c>
       <c r="D80">
-        <v>56.12236360107936</v>
+        <v>55.50603441847835</v>
       </c>
       <c r="E80">
-        <v>182.0694</v>
+        <v>184.4617</v>
       </c>
       <c r="F80">
-        <v>186.5994</v>
+        <v>188.9917</v>
       </c>
       <c r="G80">
         <v>4.46</v>
@@ -7835,37 +7835,37 @@
         <v>14.83</v>
       </c>
       <c r="M80">
-        <v>44.00013852</v>
+        <v>44.56424286000001</v>
       </c>
       <c r="N80">
-        <v>-29.17013852</v>
+        <v>-29.73424286000001</v>
       </c>
       <c r="O80">
-        <v>-7.29253463</v>
+        <v>-7.433560715000002</v>
       </c>
       <c r="P80">
-        <v>-21.87760389</v>
+        <v>-22.30068214500001</v>
       </c>
       <c r="Q80">
-        <v>-18.70760389</v>
+        <v>-19.13068214500001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2203903437830201</v>
+        <v>0.2287041696774496</v>
       </c>
       <c r="T80">
-        <v>3.499429486094991</v>
+        <v>3.666068985432848</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.08426109836710578</v>
+        <v>0.08319450218524367</v>
       </c>
       <c r="W80">
-        <v>0.2159312330050364</v>
+        <v>0.2161827363847195</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3370443934684231</v>
+        <v>0.3327780087409746</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2188122373761928</v>
+        <v>0.2207122373761929</v>
       </c>
       <c r="C81">
-        <v>-129.0256655815217</v>
+        <v>-132.020904901132</v>
       </c>
       <c r="D81">
-        <v>55.50603441847835</v>
+        <v>54.90309509886804</v>
       </c>
       <c r="E81">
-        <v>184.4617</v>
+        <v>186.854</v>
       </c>
       <c r="F81">
-        <v>188.9917</v>
+        <v>191.384</v>
       </c>
       <c r="G81">
         <v>4.46</v>
@@ -7917,37 +7917,37 @@
         <v>14.83</v>
       </c>
       <c r="M81">
-        <v>44.56424286000001</v>
+        <v>45.12834720000001</v>
       </c>
       <c r="N81">
-        <v>-29.73424286000001</v>
+        <v>-30.29834720000001</v>
       </c>
       <c r="O81">
-        <v>-7.433560715000002</v>
+        <v>-7.574586800000002</v>
       </c>
       <c r="P81">
-        <v>-22.30068214500001</v>
+        <v>-22.72376040000001</v>
       </c>
       <c r="Q81">
-        <v>-19.13068214500001</v>
+        <v>-19.55376040000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2287041696774496</v>
+        <v>0.2378493781613221</v>
       </c>
       <c r="T81">
-        <v>3.666068985432848</v>
+        <v>3.849372434704491</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.08319450218524367</v>
+        <v>0.08215457090792812</v>
       </c>
       <c r="W81">
-        <v>0.2161827363847195</v>
+        <v>0.2164279521799106</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3327780087409746</v>
+        <v>0.3286182836317124</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2207122373761929</v>
+        <v>0.2226122373761929</v>
       </c>
       <c r="C82">
-        <v>-132.020904901132</v>
+        <v>-135.0031860146331</v>
       </c>
       <c r="D82">
-        <v>54.90309509886804</v>
+        <v>54.31311398536686</v>
       </c>
       <c r="E82">
-        <v>186.854</v>
+        <v>189.2463</v>
       </c>
       <c r="F82">
-        <v>191.384</v>
+        <v>193.7763</v>
       </c>
       <c r="G82">
         <v>4.46</v>
@@ -7999,37 +7999,37 @@
         <v>14.83</v>
       </c>
       <c r="M82">
-        <v>45.12834720000001</v>
+        <v>45.69245154</v>
       </c>
       <c r="N82">
-        <v>-30.29834720000001</v>
+        <v>-30.86245154</v>
       </c>
       <c r="O82">
-        <v>-7.574586800000002</v>
+        <v>-7.715612885000001</v>
       </c>
       <c r="P82">
-        <v>-22.72376040000001</v>
+        <v>-23.146838655</v>
       </c>
       <c r="Q82">
-        <v>-19.55376040000001</v>
+        <v>-19.976838655</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2378493781613221</v>
+        <v>0.2479572401698128</v>
       </c>
       <c r="T82">
-        <v>3.849372434704491</v>
+        <v>4.051970983899465</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08215457090792812</v>
+        <v>0.08114031694610185</v>
       </c>
       <c r="W82">
-        <v>0.2164279521799106</v>
+        <v>0.2166671132641092</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3286182836317124</v>
+        <v>0.3245612677844074</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2226122373761929</v>
+        <v>0.2245122373761929</v>
       </c>
       <c r="C83">
-        <v>-135.0031860146331</v>
+        <v>-137.9729222220652</v>
       </c>
       <c r="D83">
-        <v>54.31311398536686</v>
+        <v>53.73567777793482</v>
       </c>
       <c r="E83">
-        <v>189.2463</v>
+        <v>191.6386</v>
       </c>
       <c r="F83">
-        <v>193.7763</v>
+        <v>196.1686</v>
       </c>
       <c r="G83">
         <v>4.46</v>
@@ -8081,37 +8081,37 @@
         <v>14.83</v>
       </c>
       <c r="M83">
-        <v>45.69245154</v>
+        <v>46.25655588</v>
       </c>
       <c r="N83">
-        <v>-30.86245154</v>
+        <v>-31.42655588</v>
       </c>
       <c r="O83">
-        <v>-7.715612885000001</v>
+        <v>-7.856638970000001</v>
       </c>
       <c r="P83">
-        <v>-23.146838655</v>
+        <v>-23.56991691</v>
       </c>
       <c r="Q83">
-        <v>-19.976838655</v>
+        <v>-20.39991691</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2479572401698128</v>
+        <v>0.2591881979570245</v>
       </c>
       <c r="T83">
-        <v>4.051970983899465</v>
+        <v>4.27708048300499</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08114031694610185</v>
+        <v>0.08015080088578354</v>
       </c>
       <c r="W83">
-        <v>0.2166671132641092</v>
+        <v>0.2169004411511322</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3245612677844074</v>
+        <v>0.3206032035431341</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2245122373761929</v>
+        <v>0.2264122373761929</v>
       </c>
       <c r="C84">
-        <v>-137.9729222220652</v>
+        <v>-140.930509432175</v>
       </c>
       <c r="D84">
-        <v>53.73567777793482</v>
+        <v>53.17039056782502</v>
       </c>
       <c r="E84">
-        <v>191.6386</v>
+        <v>194.0309</v>
       </c>
       <c r="F84">
-        <v>196.1686</v>
+        <v>198.5609</v>
       </c>
       <c r="G84">
         <v>4.46</v>
@@ -8163,37 +8163,37 @@
         <v>14.83</v>
       </c>
       <c r="M84">
-        <v>46.25655588</v>
+        <v>46.82066022</v>
       </c>
       <c r="N84">
-        <v>-31.42655588</v>
+        <v>-31.99066022</v>
       </c>
       <c r="O84">
-        <v>-7.856638970000001</v>
+        <v>-7.997665055000001</v>
       </c>
       <c r="P84">
-        <v>-23.56991691</v>
+        <v>-23.992995165</v>
       </c>
       <c r="Q84">
-        <v>-20.39991691</v>
+        <v>-20.822995165</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2591881979570245</v>
+        <v>0.2717404448956731</v>
       </c>
       <c r="T84">
-        <v>4.27708048300499</v>
+        <v>4.528673452593519</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08015080088578354</v>
+        <v>0.07918512858595482</v>
       </c>
       <c r="W84">
-        <v>0.2169004411511322</v>
+        <v>0.2171281466794319</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3206032035431341</v>
+        <v>0.3167405143438192</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2264122373761929</v>
+        <v>0.2283122373761929</v>
       </c>
       <c r="C85">
-        <v>-140.930509432175</v>
+        <v>-143.8763270676563</v>
       </c>
       <c r="D85">
-        <v>53.17039056782502</v>
+        <v>52.61687293234373</v>
       </c>
       <c r="E85">
-        <v>194.0309</v>
+        <v>196.4232</v>
       </c>
       <c r="F85">
-        <v>198.5609</v>
+        <v>200.9532</v>
       </c>
       <c r="G85">
         <v>4.46</v>
@@ -8245,37 +8245,37 @@
         <v>14.83</v>
       </c>
       <c r="M85">
-        <v>46.82066022</v>
+        <v>47.38476456</v>
       </c>
       <c r="N85">
-        <v>-31.99066022</v>
+        <v>-32.55476456</v>
       </c>
       <c r="O85">
-        <v>-7.997665055000001</v>
+        <v>-8.138691140000001</v>
       </c>
       <c r="P85">
-        <v>-23.992995165</v>
+        <v>-24.41607342</v>
       </c>
       <c r="Q85">
-        <v>-20.822995165</v>
+        <v>-21.24607342</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2717404448956731</v>
+        <v>0.2858617227016527</v>
       </c>
       <c r="T85">
-        <v>4.528673452593519</v>
+        <v>4.811715543380616</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.07918512858595482</v>
+        <v>0.07824244848374108</v>
       </c>
       <c r="W85">
-        <v>0.2171281466794319</v>
+        <v>0.2173504306475339</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3167405143438192</v>
+        <v>0.3129697939349643</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2283122373761929</v>
+        <v>0.2302122373761928</v>
       </c>
       <c r="C86">
-        <v>-143.8763270676562</v>
+        <v>-146.8107389144287</v>
       </c>
       <c r="D86">
-        <v>52.61687293234379</v>
+        <v>52.07476108557127</v>
       </c>
       <c r="E86">
-        <v>196.4232</v>
+        <v>198.8155</v>
       </c>
       <c r="F86">
-        <v>200.9532</v>
+        <v>203.3455</v>
       </c>
       <c r="G86">
         <v>4.46</v>
@@ -8327,37 +8327,37 @@
         <v>14.83</v>
       </c>
       <c r="M86">
-        <v>47.38476456</v>
+        <v>47.9488689</v>
       </c>
       <c r="N86">
-        <v>-32.55476456</v>
+        <v>-33.1188689</v>
       </c>
       <c r="O86">
-        <v>-8.138691140000001</v>
+        <v>-8.279717225000001</v>
       </c>
       <c r="P86">
-        <v>-24.41607342</v>
+        <v>-24.839151675</v>
       </c>
       <c r="Q86">
-        <v>-21.24607342</v>
+        <v>-21.669151675</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2858617227016525</v>
+        <v>0.3018658375484294</v>
       </c>
       <c r="T86">
-        <v>4.811715543380612</v>
+        <v>5.132496579605987</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.07824244848374108</v>
+        <v>0.07732194908981471</v>
       </c>
       <c r="W86">
-        <v>0.2173504306475339</v>
+        <v>0.2175674844046217</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3129697939349643</v>
+        <v>0.3092877963592588</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2302122373761928</v>
+        <v>0.2321122373761929</v>
       </c>
       <c r="C87">
-        <v>-146.8107389144287</v>
+        <v>-149.7340939189521</v>
       </c>
       <c r="D87">
-        <v>52.07476108557127</v>
+        <v>51.54370608104787</v>
       </c>
       <c r="E87">
-        <v>198.8155</v>
+        <v>201.2078</v>
       </c>
       <c r="F87">
-        <v>203.3455</v>
+        <v>205.7378</v>
       </c>
       <c r="G87">
         <v>4.46</v>
@@ -8409,37 +8409,37 @@
         <v>14.83</v>
       </c>
       <c r="M87">
-        <v>47.9488689</v>
+        <v>48.51297324</v>
       </c>
       <c r="N87">
-        <v>-33.1188689</v>
+        <v>-33.68297324</v>
       </c>
       <c r="O87">
-        <v>-8.279717225000001</v>
+        <v>-8.420743310000001</v>
       </c>
       <c r="P87">
-        <v>-24.839151675</v>
+        <v>-25.26222993</v>
       </c>
       <c r="Q87">
-        <v>-21.669151675</v>
+        <v>-22.09222993</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3018658375484294</v>
+        <v>0.3201562545161744</v>
       </c>
       <c r="T87">
-        <v>5.132496579605987</v>
+        <v>5.499103478149272</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.07732194908981471</v>
+        <v>0.07642285665853779</v>
       </c>
       <c r="W87">
-        <v>0.2175674844046217</v>
+        <v>0.2177794903999168</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3092877963592588</v>
+        <v>0.3056914266341512</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2321122373761929</v>
+        <v>0.2340122373761928</v>
       </c>
       <c r="C88">
-        <v>-149.7340939189521</v>
+        <v>-152.646726937247</v>
       </c>
       <c r="D88">
-        <v>51.54370608104787</v>
+        <v>51.02337306275299</v>
       </c>
       <c r="E88">
-        <v>201.2078</v>
+        <v>203.6001</v>
       </c>
       <c r="F88">
-        <v>205.7378</v>
+        <v>208.1301</v>
       </c>
       <c r="G88">
         <v>4.46</v>
@@ -8491,37 +8491,37 @@
         <v>14.83</v>
       </c>
       <c r="M88">
-        <v>48.51297324</v>
+        <v>49.07707758</v>
       </c>
       <c r="N88">
-        <v>-33.68297324</v>
+        <v>-34.24707758</v>
       </c>
       <c r="O88">
-        <v>-8.420743310000001</v>
+        <v>-8.561769395000001</v>
       </c>
       <c r="P88">
-        <v>-25.26222993</v>
+        <v>-25.685308185</v>
       </c>
       <c r="Q88">
-        <v>-22.09222993</v>
+        <v>-22.515308185</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3201562545161744</v>
+        <v>0.3412605817866493</v>
       </c>
       <c r="T88">
-        <v>5.499103478149272</v>
+        <v>5.922111438006908</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.07642285665853779</v>
+        <v>0.07554443301878448</v>
       </c>
       <c r="W88">
-        <v>0.2177794903999168</v>
+        <v>0.2179866226941706</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3056914266341512</v>
+        <v>0.3021777320751379</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2340122373761928</v>
+        <v>0.2359122373761929</v>
       </c>
       <c r="C89">
-        <v>-152.646726937247</v>
+        <v>-155.5489594390007</v>
       </c>
       <c r="D89">
-        <v>51.02337306275299</v>
+        <v>50.51344056099929</v>
       </c>
       <c r="E89">
-        <v>203.6001</v>
+        <v>205.9924</v>
       </c>
       <c r="F89">
-        <v>208.1301</v>
+        <v>210.5224</v>
       </c>
       <c r="G89">
         <v>4.46</v>
@@ -8573,37 +8573,37 @@
         <v>14.83</v>
       </c>
       <c r="M89">
-        <v>49.07707758</v>
+        <v>49.64118192</v>
       </c>
       <c r="N89">
-        <v>-34.24707758</v>
+        <v>-34.81118192</v>
       </c>
       <c r="O89">
-        <v>-8.561769395000001</v>
+        <v>-8.702795480000001</v>
       </c>
       <c r="P89">
-        <v>-25.685308185</v>
+        <v>-26.10838644</v>
       </c>
       <c r="Q89">
-        <v>-22.515308185</v>
+        <v>-22.93838644</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3412605817866493</v>
+        <v>0.3658822969355368</v>
       </c>
       <c r="T89">
-        <v>5.922111438006908</v>
+        <v>6.415620724507485</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.07554443301878448</v>
+        <v>0.07468597355266193</v>
       </c>
       <c r="W89">
-        <v>0.2179866226941706</v>
+        <v>0.2181890474362823</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3021777320751379</v>
+        <v>0.2987438942106477</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2359122373761929</v>
+        <v>0.2378122373761928</v>
       </c>
       <c r="C90">
-        <v>-155.5489594390007</v>
+        <v>-158.4411001698697</v>
       </c>
       <c r="D90">
-        <v>50.51344056099929</v>
+        <v>50.01359983013032</v>
       </c>
       <c r="E90">
-        <v>205.9924</v>
+        <v>208.3847</v>
       </c>
       <c r="F90">
-        <v>210.5224</v>
+        <v>212.9147</v>
       </c>
       <c r="G90">
         <v>4.46</v>
@@ -8655,37 +8655,37 @@
         <v>14.83</v>
       </c>
       <c r="M90">
-        <v>49.64118192</v>
+        <v>50.20528626</v>
       </c>
       <c r="N90">
-        <v>-34.81118192</v>
+        <v>-35.37528626</v>
       </c>
       <c r="O90">
-        <v>-8.702795480000001</v>
+        <v>-8.843821565000001</v>
       </c>
       <c r="P90">
-        <v>-26.10838644</v>
+        <v>-26.531464695</v>
       </c>
       <c r="Q90">
-        <v>-22.93838644</v>
+        <v>-23.361464695</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3658822969355368</v>
+        <v>0.3949806875660401</v>
       </c>
       <c r="T90">
-        <v>6.415620724507485</v>
+        <v>6.998858972189983</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.07468597355266193</v>
+        <v>0.0738468053104972</v>
       </c>
       <c r="W90">
-        <v>0.2181890474362823</v>
+        <v>0.2183869233077848</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2987438942106477</v>
+        <v>0.2953872212419888</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2378122373761928</v>
+        <v>0.2397122373761928</v>
       </c>
       <c r="C91">
-        <v>-158.4411001698697</v>
+        <v>-161.3234457748456</v>
       </c>
       <c r="D91">
-        <v>50.01359983013032</v>
+        <v>49.52355422515441</v>
       </c>
       <c r="E91">
-        <v>208.3847</v>
+        <v>210.777</v>
       </c>
       <c r="F91">
-        <v>212.9147</v>
+        <v>215.307</v>
       </c>
       <c r="G91">
         <v>4.46</v>
@@ -8737,37 +8737,37 @@
         <v>14.83</v>
       </c>
       <c r="M91">
-        <v>50.20528626</v>
+        <v>50.7693906</v>
       </c>
       <c r="N91">
-        <v>-35.37528626</v>
+        <v>-35.9393906</v>
       </c>
       <c r="O91">
-        <v>-8.843821565000001</v>
+        <v>-8.984847650000001</v>
       </c>
       <c r="P91">
-        <v>-26.531464695</v>
+        <v>-26.95454295</v>
       </c>
       <c r="Q91">
-        <v>-23.361464695</v>
+        <v>-23.78454295</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3949806875660401</v>
+        <v>0.4298987563226442</v>
       </c>
       <c r="T91">
-        <v>6.998858972189983</v>
+        <v>7.698744869408983</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0738468053104972</v>
+        <v>0.07302628525149167</v>
       </c>
       <c r="W91">
-        <v>0.2183869233077848</v>
+        <v>0.2185804019376983</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2953872212419888</v>
+        <v>0.2921051410059666</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2397122373761928</v>
+        <v>0.2416122373761928</v>
       </c>
       <c r="C92">
-        <v>-161.3234457748456</v>
+        <v>-164.1962813853295</v>
       </c>
       <c r="D92">
-        <v>49.52355422515441</v>
+        <v>49.0430186146705</v>
       </c>
       <c r="E92">
-        <v>210.777</v>
+        <v>213.1693</v>
       </c>
       <c r="F92">
-        <v>215.307</v>
+        <v>217.6993</v>
       </c>
       <c r="G92">
         <v>4.46</v>
@@ -8819,37 +8819,37 @@
         <v>14.83</v>
       </c>
       <c r="M92">
-        <v>50.7693906</v>
+        <v>51.33349494</v>
       </c>
       <c r="N92">
-        <v>-35.9393906</v>
+        <v>-36.50349494</v>
       </c>
       <c r="O92">
-        <v>-8.984847650000001</v>
+        <v>-9.125873735000001</v>
       </c>
       <c r="P92">
-        <v>-26.95454295</v>
+        <v>-27.377621205</v>
       </c>
       <c r="Q92">
-        <v>-23.78454295</v>
+        <v>-24.207621205</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4298987563226442</v>
+        <v>0.4725763959140491</v>
       </c>
       <c r="T92">
-        <v>7.698744869408983</v>
+        <v>8.554160966009981</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07302628525149167</v>
+        <v>0.07222379860037638</v>
       </c>
       <c r="W92">
-        <v>0.2185804019376983</v>
+        <v>0.2187696282900312</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2921051410059666</v>
+        <v>0.2888951944015055</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2416122373761928</v>
+        <v>0.2435122373761929</v>
       </c>
       <c r="C93">
-        <v>-164.1962813853295</v>
+        <v>-167.0598811723557</v>
       </c>
       <c r="D93">
-        <v>49.0430186146705</v>
+        <v>48.57171882764425</v>
       </c>
       <c r="E93">
-        <v>213.1693</v>
+        <v>215.5616</v>
       </c>
       <c r="F93">
-        <v>217.6993</v>
+        <v>220.0916</v>
       </c>
       <c r="G93">
         <v>4.46</v>
@@ -8901,37 +8901,37 @@
         <v>14.83</v>
       </c>
       <c r="M93">
-        <v>51.33349494</v>
+        <v>51.89759928</v>
       </c>
       <c r="N93">
-        <v>-36.50349494</v>
+        <v>-37.06759928</v>
       </c>
       <c r="O93">
-        <v>-9.125873735000001</v>
+        <v>-9.266899820000001</v>
       </c>
       <c r="P93">
-        <v>-27.377621205</v>
+        <v>-27.80069946</v>
       </c>
       <c r="Q93">
-        <v>-24.207621205</v>
+        <v>-24.63069946</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4725763959140491</v>
+        <v>0.5259234454033054</v>
       </c>
       <c r="T93">
-        <v>8.554160966009981</v>
+        <v>9.623431086761231</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07222379860037638</v>
+        <v>0.07143875731124186</v>
       </c>
       <c r="W93">
-        <v>0.2187696282900312</v>
+        <v>0.2189547410260092</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2888951944015055</v>
+        <v>0.2857550292449674</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2435122373761929</v>
+        <v>0.2454122373761928</v>
       </c>
       <c r="C94">
-        <v>-167.0598811723557</v>
+        <v>-169.9145088682204</v>
       </c>
       <c r="D94">
-        <v>48.57171882764425</v>
+        <v>48.10939113177961</v>
       </c>
       <c r="E94">
-        <v>215.5616</v>
+        <v>217.9539</v>
       </c>
       <c r="F94">
-        <v>220.0916</v>
+        <v>222.4839</v>
       </c>
       <c r="G94">
         <v>4.46</v>
@@ -8983,37 +8983,37 @@
         <v>14.83</v>
       </c>
       <c r="M94">
-        <v>51.89759928</v>
+        <v>52.46170362</v>
       </c>
       <c r="N94">
-        <v>-37.06759928</v>
+        <v>-37.63170362</v>
       </c>
       <c r="O94">
-        <v>-9.266899820000001</v>
+        <v>-9.407925905000001</v>
       </c>
       <c r="P94">
-        <v>-27.80069946</v>
+        <v>-28.223777715</v>
       </c>
       <c r="Q94">
-        <v>-24.63069946</v>
+        <v>-25.053777715</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5259234454033054</v>
+        <v>0.594512509032349</v>
       </c>
       <c r="T94">
-        <v>9.623431086761231</v>
+        <v>10.99820695629855</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07143875731124186</v>
+        <v>0.07067059863047581</v>
       </c>
       <c r="W94">
-        <v>0.2189547410260092</v>
+        <v>0.2191358728429338</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2857550292449674</v>
+        <v>0.2826823945219032</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2454122373761928</v>
+        <v>0.2473122373761928</v>
       </c>
       <c r="C95">
-        <v>-169.9145088682204</v>
+        <v>-172.7604182586007</v>
       </c>
       <c r="D95">
-        <v>48.10939113177961</v>
+        <v>47.65578174139934</v>
       </c>
       <c r="E95">
-        <v>217.9539</v>
+        <v>220.3462</v>
       </c>
       <c r="F95">
-        <v>222.4839</v>
+        <v>224.8762</v>
       </c>
       <c r="G95">
         <v>4.46</v>
@@ -9065,37 +9065,37 @@
         <v>14.83</v>
       </c>
       <c r="M95">
-        <v>52.46170362</v>
+        <v>53.02580796</v>
       </c>
       <c r="N95">
-        <v>-37.63170362</v>
+        <v>-38.19580796</v>
       </c>
       <c r="O95">
-        <v>-9.407925905000001</v>
+        <v>-9.548951990000001</v>
       </c>
       <c r="P95">
-        <v>-28.223777715</v>
+        <v>-28.64685597</v>
       </c>
       <c r="Q95">
-        <v>-25.053777715</v>
+        <v>-25.47685597</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.594512509032349</v>
+        <v>0.685964593871074</v>
       </c>
       <c r="T95">
-        <v>10.99820695629855</v>
+        <v>12.83124144901498</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07067059863047581</v>
+        <v>0.0699187837514282</v>
       </c>
       <c r="W95">
-        <v>0.2191358728429338</v>
+        <v>0.2193131507914132</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2826823945219032</v>
+        <v>0.2796751350057127</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2473122373761928</v>
+        <v>0.2492122373761929</v>
       </c>
       <c r="C96">
-        <v>-172.7604182586007</v>
+        <v>-175.5978536470936</v>
       </c>
       <c r="D96">
-        <v>47.65578174139934</v>
+        <v>47.21064635290644</v>
       </c>
       <c r="E96">
-        <v>220.3462</v>
+        <v>222.7385</v>
       </c>
       <c r="F96">
-        <v>224.8762</v>
+        <v>227.2685</v>
       </c>
       <c r="G96">
         <v>4.46</v>
@@ -9147,37 +9147,37 @@
         <v>14.83</v>
       </c>
       <c r="M96">
-        <v>53.02580796</v>
+        <v>53.58991230000001</v>
       </c>
       <c r="N96">
-        <v>-38.19580796</v>
+        <v>-38.75991230000001</v>
       </c>
       <c r="O96">
-        <v>-9.548951990000001</v>
+        <v>-9.689978075000003</v>
       </c>
       <c r="P96">
-        <v>-28.64685597</v>
+        <v>-29.06993422500001</v>
       </c>
       <c r="Q96">
-        <v>-25.47685597</v>
+        <v>-25.89993422500001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.685964593871074</v>
+        <v>0.8139975126452893</v>
       </c>
       <c r="T96">
-        <v>12.83124144901498</v>
+        <v>15.39748973881798</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0699187837514282</v>
+        <v>0.06918279655404473</v>
       </c>
       <c r="W96">
-        <v>0.2193131507914132</v>
+        <v>0.2194866965725563</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2796751350057127</v>
+        <v>0.2767311862161789</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2492122373761929</v>
+        <v>0.2511122373761929</v>
       </c>
       <c r="C97">
-        <v>-175.5978536470936</v>
+        <v>-178.4270502939611</v>
       </c>
       <c r="D97">
-        <v>47.21064635290644</v>
+        <v>46.77374970603893</v>
       </c>
       <c r="E97">
-        <v>222.7385</v>
+        <v>225.1308</v>
       </c>
       <c r="F97">
-        <v>227.2685</v>
+        <v>229.6608</v>
       </c>
       <c r="G97">
         <v>4.46</v>
@@ -9229,37 +9229,37 @@
         <v>14.83</v>
       </c>
       <c r="M97">
-        <v>53.58991230000001</v>
+        <v>54.15401664</v>
       </c>
       <c r="N97">
-        <v>-38.75991230000001</v>
+        <v>-39.32401664</v>
       </c>
       <c r="O97">
-        <v>-9.689978075000003</v>
+        <v>-9.831004160000001</v>
       </c>
       <c r="P97">
-        <v>-29.06993422500001</v>
+        <v>-29.49301248</v>
       </c>
       <c r="Q97">
-        <v>-25.89993422500001</v>
+        <v>-26.32301248</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.8139975126452893</v>
+        <v>1.006046890806612</v>
       </c>
       <c r="T97">
-        <v>15.39748973881798</v>
+        <v>19.24686217352249</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.06918279655404473</v>
+        <v>0.06846214242327345</v>
       </c>
       <c r="W97">
-        <v>0.2194866965725563</v>
+        <v>0.2196566268165921</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2767311862161789</v>
+        <v>0.2738485696930937</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2511122373761929</v>
+        <v>0.2530122373761928</v>
       </c>
       <c r="C98">
-        <v>-178.4270502939611</v>
+        <v>-181.2482348307373</v>
       </c>
       <c r="D98">
-        <v>46.77374970603893</v>
+        <v>46.34486516926263</v>
       </c>
       <c r="E98">
-        <v>225.1308</v>
+        <v>227.5231</v>
       </c>
       <c r="F98">
-        <v>229.6608</v>
+        <v>232.0531</v>
       </c>
       <c r="G98">
         <v>4.46</v>
@@ -9311,37 +9311,37 @@
         <v>14.83</v>
       </c>
       <c r="M98">
-        <v>54.15401664</v>
+        <v>54.71812097999999</v>
       </c>
       <c r="N98">
-        <v>-39.32401664</v>
+        <v>-39.88812098</v>
       </c>
       <c r="O98">
-        <v>-9.831004160000001</v>
+        <v>-9.972030244999999</v>
       </c>
       <c r="P98">
-        <v>-29.49301248</v>
+        <v>-29.916090735</v>
       </c>
       <c r="Q98">
-        <v>-26.32301248</v>
+        <v>-26.746090735</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.006046890806609</v>
+        <v>1.326129187742146</v>
       </c>
       <c r="T98">
-        <v>19.24686217352243</v>
+        <v>25.66248289802991</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.06846214242327345</v>
+        <v>0.06775634714055929</v>
       </c>
       <c r="W98">
-        <v>0.2196566268165921</v>
+        <v>0.2198230533442561</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2738485696930937</v>
+        <v>0.2710253885622371</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2530122373761928</v>
+        <v>0.2549122373761928</v>
       </c>
       <c r="C99">
-        <v>-181.2482348307373</v>
+        <v>-184.0616256522333</v>
       </c>
       <c r="D99">
-        <v>46.34486516926263</v>
+        <v>45.92377434776667</v>
       </c>
       <c r="E99">
-        <v>227.5231</v>
+        <v>229.9154</v>
       </c>
       <c r="F99">
-        <v>232.0531</v>
+        <v>234.4454</v>
       </c>
       <c r="G99">
         <v>4.46</v>
@@ -9393,37 +9393,37 @@
         <v>14.83</v>
       </c>
       <c r="M99">
-        <v>54.71812097999999</v>
+        <v>55.28222531999999</v>
       </c>
       <c r="N99">
-        <v>-39.88812098</v>
+        <v>-40.45222532</v>
       </c>
       <c r="O99">
-        <v>-9.972030244999999</v>
+        <v>-10.11305633</v>
       </c>
       <c r="P99">
-        <v>-29.916090735</v>
+        <v>-30.33916899</v>
       </c>
       <c r="Q99">
-        <v>-26.746090735</v>
+        <v>-27.16916899</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.326129187742146</v>
+        <v>1.966293781613219</v>
       </c>
       <c r="T99">
-        <v>25.66248289802991</v>
+        <v>38.49372434704487</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.06775634714055929</v>
+        <v>0.06706495584320664</v>
       </c>
       <c r="W99">
-        <v>0.2198230533442561</v>
+        <v>0.2199860834121719</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2710253885622371</v>
+        <v>0.2682598233728265</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2549122373761928</v>
+        <v>0.2568122373761929</v>
       </c>
       <c r="C100">
-        <v>-184.0616256522333</v>
+        <v>-186.8674332873625</v>
       </c>
       <c r="D100">
-        <v>45.92377434776667</v>
+        <v>45.51026671263745</v>
       </c>
       <c r="E100">
-        <v>229.9154</v>
+        <v>232.3077</v>
       </c>
       <c r="F100">
-        <v>234.4454</v>
+        <v>236.8377</v>
       </c>
       <c r="G100">
         <v>4.46</v>
@@ -9475,37 +9475,37 @@
         <v>14.83</v>
       </c>
       <c r="M100">
-        <v>55.28222531999999</v>
+        <v>55.84632965999999</v>
       </c>
       <c r="N100">
-        <v>-40.45222532</v>
+        <v>-41.01632966</v>
       </c>
       <c r="O100">
-        <v>-10.11305633</v>
+        <v>-10.254082415</v>
       </c>
       <c r="P100">
-        <v>-30.33916899</v>
+        <v>-30.762247245</v>
       </c>
       <c r="Q100">
-        <v>-27.16916899</v>
+        <v>-27.592247245</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.966293781613219</v>
+        <v>3.886787563226437</v>
       </c>
       <c r="T100">
-        <v>38.49372434704487</v>
+        <v>76.98744869408974</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.06706495584320664</v>
+        <v>0.06638753204681062</v>
       </c>
       <c r="W100">
-        <v>0.2199860834121719</v>
+        <v>0.2201458199433621</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2682598233728265</v>
+        <v>0.2655501281872424</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2568122373761929</v>
-      </c>
-      <c r="C101">
-        <v>-186.8674332873625</v>
-      </c>
-      <c r="D101">
-        <v>45.51026671263745</v>
-      </c>
-      <c r="E101">
-        <v>232.3077</v>
-      </c>
-      <c r="F101">
-        <v>236.8377</v>
-      </c>
-      <c r="G101">
-        <v>4.46</v>
-      </c>
-      <c r="H101">
-        <v>234.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>18</v>
-      </c>
-      <c r="K101">
-        <v>3.17</v>
-      </c>
-      <c r="L101">
-        <v>14.83</v>
-      </c>
-      <c r="M101">
-        <v>55.84632965999999</v>
-      </c>
-      <c r="N101">
-        <v>-41.01632966</v>
-      </c>
-      <c r="O101">
-        <v>-10.254082415</v>
-      </c>
-      <c r="P101">
-        <v>-30.762247245</v>
-      </c>
-      <c r="Q101">
-        <v>-27.592247245</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.886787563226437</v>
-      </c>
-      <c r="T101">
-        <v>76.98744869408974</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.06638753204681062</v>
-      </c>
-      <c r="W101">
-        <v>0.2201458199433621</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2655501281872424</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
